--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-08 09:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -885,17 +885,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>80'079.94</t>
+          <t>79'779.94</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.2244</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1</v>
+        <v>0.9963</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5346</v>
+        <v>0.5332</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>28'538.99</t>
+          <t>28'525.54</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
         <v>0.5657</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3564</v>
+        <v>0.3562</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.482</v>
+        <v>0.4819</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1425,17 +1425,17 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>5'676.21</t>
+          <t>5'665.38</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
         <v>0.6425</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0709</v>
+        <v>0.0707</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.4139</v>
+        <v>0.4138</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1984,58 +1984,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>6'459.33</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.4997</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.3682</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.3366</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2044,58 +2044,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>6'459.33</t>
+          <t>10'721.17</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.4613</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1339</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3321</v>
+        <v>0.3303</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 01 Sep 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 16 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-08 09:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,126 +2221,306 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02591</t>
+          <t>CM-26-02698</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>16.67%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>12'825.56</t>
+          <t>44'496.24</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1</v>
+        <v>0.0342</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1602</v>
+        <v>0.5556</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.6641</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-02674</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Hosanna</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Hosanna</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>3'813.96</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>0.1764</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0.1249</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-02682</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Latour</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Château Latour</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>9'515.00</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.063</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-02676</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Latour</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Château Latour</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6" t="n">
+      <c r="L7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-02695</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N5"/>
+  <autoFilter ref="A3:N8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2355,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2377,14 +2557,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 09 Aug 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 24 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-08 09:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2522,11 +2702,11 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02364</t>
+          <t>CM-26-02698</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2536,117 +2716,117 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>80'079.94</t>
+          <t>44'496.24</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.2244</v>
+        <v>0.0342</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1</v>
+        <v>0.5556</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5346</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02379</t>
+          <t>CM-26-02476</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>111</v>
+        <v>1003</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>80'079.93</t>
+          <t>32'358.75</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.108</v>
+        <v>0.096</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1</v>
+        <v>0.4041</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.4648</v>
+        <v>0.2192</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02440</t>
+          <t>CM-26-02475</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2656,237 +2836,237 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>117</v>
+        <v>1015</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>23'469.59</t>
+          <t>25'984.56</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2561</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2931</v>
+        <v>0.3245</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2709</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02464</t>
+          <t>CM-26-02674</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Hosanna</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Hosanna</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>475</v>
+        <v>68</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>44'390.76</t>
+          <t>3'813.96</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0252</v>
+        <v>0.1764</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5543</v>
+        <v>0.0476</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2368</v>
+        <v>0.1249</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02348</t>
+          <t>CM-26-02618</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>1'650.84</t>
+          <t>11'370.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.3527</v>
+        <v>0.0444</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.142</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2199</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02476</t>
+          <t>CM-26-02514</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Veuve Clicquot Ponsardin</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1003</v>
+        <v>66</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>32'382.95</t>
+          <t>4'283.11</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.096</v>
+        <v>0.0912</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4044</v>
+        <v>0.0535</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2194</v>
+        <v>0.0761</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02475</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2896,57 +3076,57 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>741</v>
+        <v>58</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>20'526.96</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.081</v>
+        <v>0.1032</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.2563</v>
+        <v>0.0266</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1511</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02465</t>
+          <t>CM-26-02682</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2956,247 +3136,243 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>25'407.38</t>
+          <t>9'515.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.024</v>
+        <v>0.0258</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3173</v>
+        <v>0.1188</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1413</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02409</t>
+          <t>CM-26-02549</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Tenuta Nuova</t>
+          <t>Muga Prado Enea Gran Reserva</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Casanova di Neri</t>
+          <t>Bodegas Muga</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>380</v>
+        <v>1890</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>12'929.87</t>
+          <t>1'886.06</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.0156</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1615</v>
+        <v>0.0236</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1406</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02357</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2'878.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1146</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.08309999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02514</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Veuve Clicquot Ponsardin</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>4'283.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0912</v>
+        <v>0</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0535</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02370</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -3206,342 +3382,42 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>611.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0076</v>
+        <v>0</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0696</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>108</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02358</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>La Nieta</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Viñedos de Páganos</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>1308</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>3'569.69</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.0446</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0.0344</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02549</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Muga Prado Enea Gran Reserva</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Bodegas Muga</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>783</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>0.13%</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>397.37</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0.0067</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02593</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Bonnes-Mares</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Bruno Clair</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02463</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>DRC Romanée St. Vivant</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02406</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Armand Rousseau</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>775</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N21"/>
+  <autoFilter ref="A3:N16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3556,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N156"/>
+  <dimension ref="A1:N163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3585,7 +3461,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-08 09:33  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -3948,17 +3824,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>80'079.94</t>
+          <t>79'779.94</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.2244</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1</v>
+        <v>0.9963</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5346</v>
+        <v>0.5332</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -4188,17 +4064,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>28'538.99</t>
+          <t>28'525.54</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
         <v>0.5657</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3564</v>
+        <v>0.3562</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.482</v>
+        <v>0.4819</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -4488,17 +4364,17 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>5'676.21</t>
+          <t>5'665.38</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
         <v>0.6425</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0709</v>
+        <v>0.0707</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.4139</v>
+        <v>0.4138</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -5047,58 +4923,58 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01429</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>8.33%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>29'483.52</t>
+          <t>6'459.33</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.4997</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.3682</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.3366</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -5107,58 +4983,58 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01429</t>
+          <t>CM-26-01241</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>8.33%</t>
+          <t>7.69%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>6'459.33</t>
+          <t>10'721.17</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4997</v>
+        <v>0.4613</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1339</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3321</v>
+        <v>0.3303</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -5167,58 +5043,58 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01241</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>10'721.17</t>
+          <t>27'251.02</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0.4613</v>
+        <v>0.3155</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>0.1339</v>
+        <v>0.3403</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.3303</v>
+        <v>0.3254</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -5688,17 +5564,17 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>23'469.59</t>
+          <t>23'409.83</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
         <v>0.2561</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.2931</v>
+        <v>0.2923</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2709</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -5887,58 +5763,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-02698</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>23'619.73</t>
+          <t>44'496.24</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.1986</v>
+        <v>0.0342</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.295</v>
+        <v>0.5556</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2372</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -5947,58 +5823,58 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02464</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>475</v>
+        <v>181</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>44'390.76</t>
+          <t>23'619.73</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0252</v>
+        <v>0.1986</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.5543</v>
+        <v>0.295</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.2368</v>
+        <v>0.2372</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6007,58 +5883,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02348</t>
+          <t>CM-26-02464</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>34</v>
+        <v>475</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>1'650.84</t>
+          <t>44'390.76</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.3527</v>
+        <v>0.0252</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.0206</v>
+        <v>0.5543</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.2199</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6067,58 +5943,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02476</t>
+          <t>CM-26-02348</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Finca El Bosque</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Viñedos y Bodegas Sierra Cantabria</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1003</v>
+        <v>34</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>5.88%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>32'382.95</t>
+          <t>1'650.84</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.096</v>
+        <v>0.3527</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.4044</v>
+        <v>0.0206</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.2194</v>
+        <v>0.2199</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6127,58 +6003,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-02476</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>76</v>
+        <v>1003</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>5'768.84</t>
+          <t>32'358.75</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.3155</v>
+        <v>0.096</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.4041</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2181</v>
+        <v>0.2192</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6187,58 +6063,58 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>5'768.84</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.1472</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.2154</v>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6247,58 +6123,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02022</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Kayli Morgan Vineyard</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Hundred Acre</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>6'911.52</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.2999</v>
+        <v>0.2609</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.0863</v>
+        <v>0.1472</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.2145</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6307,7 +6183,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-02022</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6317,48 +6193,48 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Kayli Morgan Vineyard</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Hundred Acre</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>6'911.52</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.2501</v>
+        <v>0.2999</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.1609</v>
+        <v>0.0863</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.2144</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6367,7 +6243,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6377,48 +6253,48 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>17'002.84</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.2154</v>
+        <v>0.2501</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.2123</v>
+        <v>0.1609</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.2144</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6427,58 +6303,58 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>17'002.84</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.036</v>
+        <v>0.2154</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.4654</v>
+        <v>0.2123</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.2078</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6487,58 +6363,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>9'698.33</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.036</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.1211</v>
+        <v>0.4654</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.205</v>
+        <v>0.2078</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6547,58 +6423,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>9'339.37</t>
+          <t>9'698.33</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.2555</v>
+        <v>0.2609</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.1166</v>
+        <v>0.1211</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.1999</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -6607,58 +6483,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>12'664.03</t>
+          <t>9'339.37</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.2555</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.1581</v>
+        <v>0.1166</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1954</v>
+        <v>0.1999</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -6667,58 +6543,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>12'664.03</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.201</v>
+        <v>0.2202</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.1822</v>
+        <v>0.1581</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1935</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -6727,58 +6603,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>10'560.34</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.222</v>
+        <v>0.201</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1319</v>
+        <v>0.1822</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.186</v>
+        <v>0.1935</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -6787,58 +6663,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>10'560.34</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.222</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.0443</v>
+        <v>0.1319</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1815</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -6847,58 +6723,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02108</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>21'336.21</t>
+          <t>3'550.60</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.12</v>
+        <v>0.2729</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.2664</v>
+        <v>0.0443</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.1786</v>
+        <v>0.1815</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -6907,58 +6783,58 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-26-02108</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>221</v>
+        <v>50</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>16'049.68</t>
+          <t>21'336.21</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.1626</v>
+        <v>0.12</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.2004</v>
+        <v>0.2664</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.1777</v>
+        <v>0.1786</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -7027,7 +6903,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-02475</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7037,48 +6913,48 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>156</v>
+        <v>1015</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>25'984.56</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.1926</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.1494</v>
+        <v>0.3245</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.1753</v>
+        <v>0.1759</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7087,58 +6963,58 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02144</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Lavaux St. Jacques</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>4'860.00</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.1926</v>
       </c>
       <c r="M61" s="6" t="n">
-        <v>0.0607</v>
+        <v>0.1494</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>0.1743</v>
+        <v>0.1753</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -7147,7 +7023,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7157,48 +7033,48 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>940</v>
+        <v>221</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>24'269.30</t>
+          <t>15'539.38</t>
         </is>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.1626</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.3031</v>
+        <v>0.194</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.1634</v>
+        <v>0.1752</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -7207,7 +7083,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-02144</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -7217,48 +7093,48 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Gevrey Chambertin Lavaux St. Jacques</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>17'433.26</t>
+          <t>4'860.00</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.2501</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.2177</v>
+        <v>0.0607</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.163</v>
+        <v>0.1743</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -7267,58 +7143,58 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>73</v>
+        <v>940</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>1'277.97</t>
+          <t>24'269.30</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.2466</v>
+        <v>0.0702</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.016</v>
+        <v>0.3031</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.1544</v>
+        <v>0.1634</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -7327,58 +7203,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02475</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>741</v>
+        <v>95</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>20'526.96</t>
+          <t>16'003.16</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.081</v>
+        <v>0.1266</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.2563</v>
+        <v>0.1998</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.1511</v>
+        <v>0.1559</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7387,7 +7263,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7397,7 +7273,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -7407,38 +7283,38 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Domaine Henri Gouges</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.222</v>
+        <v>0.2466</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.0412</v>
+        <v>0.016</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.1497</v>
+        <v>0.1544</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7447,58 +7323,58 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Henri Gouges</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.222</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.3023</v>
+        <v>0.0412</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.1486</v>
+        <v>0.1497</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7507,58 +7383,58 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>2'246.57</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.2244</v>
+        <v>0.0462</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.0281</v>
+        <v>0.3023</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.1459</v>
+        <v>0.1486</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -7567,58 +7443,58 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>2'246.57</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.2244</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.1596</v>
+        <v>0.0281</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.1456</v>
+        <v>0.1459</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -7627,58 +7503,58 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02465</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>248</v>
+        <v>88</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>25'407.38</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.024</v>
+        <v>0.1362</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.3173</v>
+        <v>0.1596</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.1413</v>
+        <v>0.1456</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -7687,58 +7563,58 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02409</t>
+          <t>CM-26-02465</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Tenuta Nuova</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Casanova di Neri</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>380</v>
+        <v>248</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>12'929.87</t>
+          <t>25'407.38</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.024</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0.1615</v>
+        <v>0.3173</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0.1406</v>
+        <v>0.1413</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -7747,58 +7623,58 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-02409</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Brunello di Montalcino Tenuta Nuova</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Casanova di Neri</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>28</v>
+        <v>380</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>1'616.38</t>
+          <t>12'911.34</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.1266</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.0202</v>
+        <v>0.1612</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.1366</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -7807,58 +7683,58 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02226</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>9'090.00</t>
+          <t>1'616.38</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0.1398</v>
+        <v>0.2142</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0.1135</v>
+        <v>0.0202</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.1293</v>
+        <v>0.1366</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -7867,7 +7743,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-02226</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -7877,48 +7753,48 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>313</v>
+        <v>43</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>9'090.00</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.1398</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.282</v>
+        <v>0.1135</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.1243</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -7927,58 +7803,58 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-02674</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Hosanna</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château Hosanna</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>3'813.96</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0.1332</v>
+        <v>0.1764</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0.1013</v>
+        <v>0.0476</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.1204</v>
+        <v>0.1249</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -7987,58 +7863,58 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.12</v>
+        <v>0.0192</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.1163</v>
+        <v>0.282</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.1185</v>
+        <v>0.1243</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -8047,58 +7923,58 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>12'828.11</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0.081</v>
+        <v>0.1332</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>0.1602</v>
+        <v>0.1013</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>0.1127</v>
+        <v>0.1204</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -8107,58 +7983,58 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.0936</v>
+        <v>0.12</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.1337</v>
+        <v>0.1163</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1185</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -8167,7 +8043,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02151</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -8177,48 +8053,48 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>La Romanée</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>11'000.00</t>
+          <t>12'828.11</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.081</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0.1374</v>
+        <v>0.1602</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0.1079</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -8227,58 +8103,58 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.0936</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.1078</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -8287,7 +8163,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-02151</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -8297,48 +8173,48 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>La Romanée</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>11'135.73</t>
+          <t>11'000.00</t>
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0882</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>0.1391</v>
+        <v>0.1374</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>0.1064</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -8347,7 +8223,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8357,7 +8233,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -8367,38 +8243,38 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>12'111.33</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.0756</v>
+        <v>0.1218</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.1512</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.1058</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -8407,7 +8283,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -8417,48 +8293,48 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>11'135.73</t>
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>0.0912</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>0.1262</v>
+        <v>0.1391</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>0.1052</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -8467,58 +8343,58 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>12'111.33</t>
         </is>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.0756</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.1512</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.1047</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -8527,58 +8403,58 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L85" s="6" t="n">
-        <v>0.132</v>
+        <v>0.0912</v>
       </c>
       <c r="M85" s="6" t="n">
-        <v>0.0586</v>
+        <v>0.1262</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>0.1026</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -8587,58 +8463,58 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>8'407.01</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.099</v>
+        <v>0.1266</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.105</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.1014</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -8647,58 +8523,58 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>13'791.85</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L87" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.132</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>0.1722</v>
+        <v>0.0586</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>0.0998</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -8707,58 +8583,58 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02291</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>440</v>
+        <v>121</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>18'010.29</t>
+          <t>8'407.01</t>
         </is>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.0138</v>
+        <v>0.099</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.2249</v>
+        <v>0.105</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>0.0982</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -8767,58 +8643,58 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02232</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Léoville Las Cases</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>11'683.71</t>
+          <t>13'791.85</t>
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0516</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>0.1459</v>
+        <v>0.1722</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>0.0969</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -8827,58 +8703,58 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-26-02291</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>87</v>
+        <v>440</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>2'424.17</t>
+          <t>18'010.29</t>
         </is>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0138</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.2249</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -8887,22 +8763,22 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-02232</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
@@ -8912,33 +8788,33 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>487</v>
+        <v>281</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>11'683.71</t>
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>0.1805</v>
+        <v>0.1459</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>0.0945</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -8947,58 +8823,58 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2'724.45</t>
+          <t>2'424.17</t>
         </is>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.138</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>0.034</v>
+        <v>0.0303</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -9007,7 +8883,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -9017,48 +8893,48 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>68</v>
+        <v>487</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>7'370.74</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0372</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>0.092</v>
+        <v>0.1805</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -9067,58 +8943,58 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>68</v>
+        <v>235</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>7'018.00</t>
+          <t>2'724.45</t>
         </is>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.1278</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.0876</v>
+        <v>0.034</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.09030000000000001</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -9127,58 +9003,58 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02357</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2'878.30</t>
+          <t>7'370.74</t>
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>0.1146</v>
+        <v>0.0882</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>0.0359</v>
+        <v>0.092</v>
       </c>
       <c r="N95" s="6" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -9187,58 +9063,58 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-02618</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>476</v>
+        <v>135</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>11'370.00</t>
         </is>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.0504</v>
+        <v>0.0444</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.1317</v>
+        <v>0.142</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.0829</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -9247,58 +9123,58 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-02357</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>La Nieta</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Viñedos de Páganos</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>268</v>
+        <v>157</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>2'869.98</t>
         </is>
       </c>
       <c r="L97" s="6" t="n">
-        <v>0.045</v>
+        <v>0.1146</v>
       </c>
       <c r="M97" s="6" t="n">
-        <v>0.1359</v>
+        <v>0.0358</v>
       </c>
       <c r="N97" s="6" t="n">
-        <v>0.0814</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -9307,58 +9183,58 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02514</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Veuve Clicquot Ponsardin</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>66</v>
+        <v>476</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>4'283.11</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.0504</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.0535</v>
+        <v>0.1317</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -9367,58 +9243,58 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="I99" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>697.16</t>
+          <t>5'945.00</t>
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.0882</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0742</v>
       </c>
       <c r="N99" s="6" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -9427,58 +9303,58 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.045</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.1359</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -9487,58 +9363,58 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02158</t>
+          <t>CM-26-02514</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Prieuré Roch</t>
+          <t>Veuve Clicquot Ponsardin</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>273</v>
+        <v>66</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>11'314.66</t>
+          <t>4'283.11</t>
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0912</v>
       </c>
       <c r="M101" s="6" t="n">
-        <v>0.1413</v>
+        <v>0.0535</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>0.0698</v>
+        <v>0.0761</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -9547,58 +9423,58 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02370</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>611.10</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.111</v>
+        <v>0.1032</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.0076</v>
+        <v>0.0266</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -9607,58 +9483,58 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02154</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Morey St. Denis Clos de la Bussière</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>7'898.70</t>
+          <t>697.16</t>
         </is>
       </c>
       <c r="L103" s="6" t="n">
-        <v>0.0414</v>
+        <v>0.1134</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>0.0643</v>
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -9667,17 +9543,17 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01755</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Echézeaux</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -9687,38 +9563,38 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>8'422.42</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.0276</v>
+        <v>0.0774</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.1052</v>
+        <v>0.0625</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>0.0586</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -9727,58 +9603,58 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-02158</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Domaine du Prieuré Roch</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2'329.50</t>
+          <t>11'314.66</t>
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="M105" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.1413</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>0.0545</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -9787,58 +9663,58 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-02370</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Finca El Bosque</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Viñedos y Bodegas Sierra Cantabria</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="I106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>3'049.20</t>
+          <t>611.10</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.06</v>
+        <v>0.111</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.0381</v>
+        <v>0.0076</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.0512</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -9847,58 +9723,58 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-02154</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Morey St. Denis Clos de la Bussière</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2'848.18</t>
+          <t>7'898.70</t>
         </is>
       </c>
       <c r="L107" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.0414</v>
       </c>
       <c r="M107" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>0.051</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -9907,58 +9783,58 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-02682</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H108" s="4" t="n">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>3'361.28</t>
+          <t>9'515.00</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.0468</v>
+        <v>0.0258</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.042</v>
+        <v>0.1188</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.0449</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -9967,7 +9843,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02200</t>
+          <t>CM-26-01755</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -9977,48 +9853,48 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Charmes Chambertin V.V.</t>
+          <t>Echézeaux</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Domaine Perrot Minot</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="I109" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>4'920.00</t>
+          <t>8'422.42</t>
         </is>
       </c>
       <c r="L109" s="6" t="n">
-        <v>0.0336</v>
+        <v>0.0276</v>
       </c>
       <c r="M109" s="6" t="n">
-        <v>0.0614</v>
+        <v>0.1052</v>
       </c>
       <c r="N109" s="6" t="n">
-        <v>0.0447</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -10027,7 +9903,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -10037,48 +9913,48 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H110" s="4" t="n">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>2'329.50</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0291</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>0.0369</v>
+        <v>0.0545</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -10087,58 +9963,58 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02358</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
-        <v>1308</v>
+        <v>393</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>3'569.69</t>
+          <t>2'848.18</t>
         </is>
       </c>
       <c r="L111" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0612</v>
       </c>
       <c r="M111" s="6" t="n">
-        <v>0.0446</v>
+        <v>0.0356</v>
       </c>
       <c r="N111" s="6" t="n">
-        <v>0.0344</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -10147,7 +10023,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -10157,48 +10033,48 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H112" s="4" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="I112" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>4'180.96</t>
+          <t>2'520.00</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.06</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.0522</v>
+        <v>0.0315</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -10207,7 +10083,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -10217,48 +10093,48 @@
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="I113" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>1'893.50</t>
+          <t>3'361.28</t>
         </is>
       </c>
       <c r="L113" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>0.0236</v>
+        <v>0.042</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>0.0318</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -10267,58 +10143,58 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02227</t>
+          <t>CM-26-02200</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Charmes Chambertin V.V.</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine Perrot Minot</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H114" s="4" t="n">
-        <v>478</v>
+        <v>177</v>
       </c>
       <c r="I114" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>3'879.31</t>
+          <t>4'920.00</t>
         </is>
       </c>
       <c r="L114" s="4" t="n">
-        <v>0.0126</v>
+        <v>0.0336</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>0.0484</v>
+        <v>0.0614</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>0.0269</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -10327,17 +10203,17 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -10356,29 +10232,29 @@
         </is>
       </c>
       <c r="H115" s="6" t="n">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L115" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0372</v>
       </c>
       <c r="M115" s="6" t="n">
-        <v>0.0071</v>
+        <v>0.0364</v>
       </c>
       <c r="N115" s="6" t="n">
-        <v>0.0158</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -10387,7 +10263,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-02358</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -10397,48 +10273,48 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>La Nieta</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Viñedos de Páganos</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H116" s="4" t="n">
-        <v>483</v>
+        <v>1308</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>968.26</t>
+          <t>3'555.07</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.0126</v>
+        <v>0.0276</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.0121</v>
+        <v>0.0444</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -10447,58 +10323,58 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02549</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Muga Prado Enea Gran Reserva</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Muga</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
-        <v>783</v>
+        <v>271</v>
       </c>
       <c r="I117" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>397.37</t>
+          <t>4'180.96</t>
         </is>
       </c>
       <c r="L117" s="6" t="n">
-        <v>0.0078</v>
+        <v>0.0222</v>
       </c>
       <c r="M117" s="6" t="n">
-        <v>0.005</v>
+        <v>0.0522</v>
       </c>
       <c r="N117" s="6" t="n">
-        <v>0.0067</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -10507,58 +10383,58 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H118" s="4" t="n">
-        <v>26</v>
+        <v>324</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'893.50</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>0</v>
+        <v>0.0372</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>0</v>
+        <v>0.0236</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>0</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -10567,7 +10443,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-02227</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -10577,48 +10453,48 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
-        <v>28</v>
+        <v>478</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3'879.31</t>
         </is>
       </c>
       <c r="L119" s="6" t="n">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="M119" s="6" t="n">
-        <v>0</v>
+        <v>0.0484</v>
       </c>
       <c r="N119" s="6" t="n">
-        <v>0</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -10627,58 +10503,58 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-02549</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Muga Prado Enea Gran Reserva</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Bodegas Muga</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H120" s="4" t="n">
-        <v>103</v>
+        <v>1890</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1'886.06</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0</v>
+        <v>0.0236</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -10687,58 +10563,58 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
-        <v>11</v>
+        <v>280</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L121" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M121" s="6" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="N121" s="6" t="n">
-        <v>0</v>
+        <v>0.0158</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -10747,58 +10623,58 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H122" s="4" t="n">
-        <v>63</v>
+        <v>483</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>968.26</t>
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0</v>
+        <v>0.0121</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -10807,7 +10683,7 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -10817,26 +10693,26 @@
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H123" s="6" t="n">
-        <v>49</v>
+        <v>252</v>
       </c>
       <c r="I123" s="6" t="n">
         <v>0</v>
@@ -10867,7 +10743,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -10877,26 +10753,26 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H124" s="4" t="n">
-        <v>543</v>
+        <v>42</v>
       </c>
       <c r="I124" s="4" t="n">
         <v>0</v>
@@ -10927,7 +10803,7 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -10937,26 +10813,26 @@
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="I125" s="6" t="n">
         <v>0</v>
@@ -10987,7 +10863,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -10997,12 +10873,12 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -11016,7 +10892,7 @@
         </is>
       </c>
       <c r="H126" s="4" t="n">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="I126" s="4" t="n">
         <v>0</v>
@@ -11047,7 +10923,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-25-02438</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -11057,26 +10933,26 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>DRC Romanée Conti</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
-        <v>75</v>
+        <v>410</v>
       </c>
       <c r="I127" s="6" t="n">
         <v>0</v>
@@ -11107,36 +10983,36 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H128" s="4" t="n">
-        <v>362</v>
+        <v>36</v>
       </c>
       <c r="I128" s="4" t="n">
         <v>0</v>
@@ -11167,7 +11043,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -11177,26 +11053,26 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H129" s="6" t="n">
-        <v>129</v>
+        <v>643</v>
       </c>
       <c r="I129" s="6" t="n">
         <v>0</v>
@@ -11227,7 +11103,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -11237,26 +11113,22 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr"/>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H130" s="4" t="n">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="I130" s="4" t="n">
         <v>0</v>
@@ -11287,7 +11159,7 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -11297,26 +11169,26 @@
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="I131" s="6" t="n">
         <v>0</v>
@@ -11347,7 +11219,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -11357,26 +11229,26 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H132" s="4" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I132" s="4" t="n">
         <v>0</v>
@@ -11407,36 +11279,36 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-01513</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
-        <v>643</v>
+        <v>22</v>
       </c>
       <c r="I133" s="6" t="n">
         <v>0</v>
@@ -11467,7 +11339,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -11477,26 +11349,26 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H134" s="4" t="n">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="I134" s="4" t="n">
         <v>0</v>
@@ -11527,7 +11399,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -11537,26 +11409,26 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H135" s="6" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="I135" s="6" t="n">
         <v>0</v>
@@ -11587,7 +11459,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01614</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -11597,12 +11469,12 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -11612,11 +11484,11 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H136" s="4" t="n">
-        <v>45</v>
+        <v>613</v>
       </c>
       <c r="I136" s="4" t="n">
         <v>0</v>
@@ -11647,7 +11519,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -11657,26 +11529,26 @@
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H137" s="6" t="n">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="I137" s="6" t="n">
         <v>0</v>
@@ -11707,12 +11579,12 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -11722,21 +11594,21 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H138" s="4" t="n">
-        <v>240</v>
+        <v>86</v>
       </c>
       <c r="I138" s="4" t="n">
         <v>0</v>
@@ -11767,7 +11639,7 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01680</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -11777,26 +11649,26 @@
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H139" s="6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I139" s="6" t="n">
         <v>0</v>
@@ -11827,36 +11699,36 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H140" s="4" t="n">
-        <v>58</v>
+        <v>716</v>
       </c>
       <c r="I140" s="4" t="n">
         <v>0</v>
@@ -11887,7 +11759,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02463</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -11897,26 +11769,26 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="I141" s="6" t="n">
         <v>0</v>
@@ -11947,36 +11819,36 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02406</t>
+          <t>CM-26-02073</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H142" s="4" t="n">
-        <v>775</v>
+        <v>223</v>
       </c>
       <c r="I142" s="4" t="n">
         <v>0</v>
@@ -12007,7 +11879,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02220</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -12017,26 +11889,26 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I143" s="6" t="n">
         <v>0</v>
@@ -12067,36 +11939,36 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02073</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H144" s="4" t="n">
-        <v>223</v>
+        <v>26</v>
       </c>
       <c r="I144" s="4" t="n">
         <v>0</v>
@@ -12127,7 +11999,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02062</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -12137,26 +12009,26 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H145" s="6" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="I145" s="6" t="n">
         <v>0</v>
@@ -12187,36 +12059,36 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01981</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Kayli Morgan Vineyard</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Hundred Acre</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H146" s="4" t="n">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I146" s="4" t="n">
         <v>0</v>
@@ -12247,7 +12119,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01614</t>
+          <t>CM-26-02220</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -12257,26 +12129,26 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
-        <v>613</v>
+        <v>10</v>
       </c>
       <c r="I147" s="6" t="n">
         <v>0</v>
@@ -12307,7 +12179,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -12317,26 +12189,26 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H148" s="4" t="n">
-        <v>716</v>
+        <v>63</v>
       </c>
       <c r="I148" s="4" t="n">
         <v>0</v>
@@ -12367,36 +12239,36 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01513</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H149" s="6" t="n">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="I149" s="6" t="n">
         <v>0</v>
@@ -12487,7 +12359,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01508</t>
+          <t>CM-26-02463</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -12497,26 +12369,26 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I151" s="6" t="n">
         <v>0</v>
@@ -12547,36 +12419,36 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H152" s="4" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I152" s="4" t="n">
         <v>0</v>
@@ -12607,7 +12479,7 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-02062</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -12617,26 +12489,26 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="I153" s="6" t="n">
         <v>0</v>
@@ -12667,36 +12539,36 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
-        <v>86</v>
+        <v>543</v>
       </c>
       <c r="I154" s="4" t="n">
         <v>0</v>
@@ -12727,7 +12599,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-01981</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -12737,26 +12609,26 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Kayli Morgan Vineyard</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Hundred Acre</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="I155" s="6" t="n">
         <v>0</v>
@@ -12787,7 +12659,7 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02438</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -12797,52 +12669,472 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée Conti</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Château Mouton Rothschild</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="I156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-00813</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>Pingus</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>Dominio de Pingus</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01680</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>DRC Richebourg</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="I158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-00728</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>Porto Vintage Nacional</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>Quinta Do Noval</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="I159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="4" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-02406</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Chambertin Clos de Bèze</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Domaine Armand Rousseau</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="n">
+        <v>775</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01477</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Chambolle-Musigny Les Amoureuses</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="I161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-00675</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>DRC Romanée St. Vivant</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="I162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01341</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>🟨</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="n">
-        <v>410</v>
-      </c>
-      <c r="I156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>Cathiard Vineyard</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K156" s="4" t="inlineStr">
+      <c r="K163" s="6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N156" s="4" t="n">
+      <c r="L163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N156"/>
+  <autoFilter ref="A3:N163"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 16 Sep 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 22 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,306 +2221,66 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02698</t>
+          <t>CM-26-02745</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>44'496.24</t>
+          <t>22'313.07</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.2142</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.5556</v>
+        <v>0.2786</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.2428</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02674</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Hosanna</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Château Hosanna</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>2.94%</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>3'813.96</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.1764</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.0476</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.1249</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02682</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Latour</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Château Latour</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>234</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>9'515.00</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.0258</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.1188</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.063</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>122</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02676</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Latour</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Château Latour</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>146</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02695</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N8"/>
+  <autoFilter ref="A3:N4"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2535,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2557,14 +2317,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 24 Aug 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 30 Aug 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2762,11 +2522,11 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02476</t>
+          <t>CM-26-02745</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -2776,113 +2536,113 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1003</v>
+        <v>84</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>32'358.75</t>
+          <t>22'313.07</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.096</v>
+        <v>0.2142</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4041</v>
+        <v>0.2786</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2192</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02475</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1015</v>
+        <v>77</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>25'984.56</t>
+          <t>18'434.16</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.3245</v>
+        <v>0.2302</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1759</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -2942,311 +2702,311 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02618</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>11'370.00</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0444</v>
+        <v>0.1032</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.142</v>
+        <v>0.0266</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0834</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02514</t>
+          <t>CM-26-02618</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Veuve Clicquot Ponsardin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>66</v>
+        <v>278</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>4'283.11</t>
+          <t>11'370.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.0216</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0535</v>
+        <v>0.142</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-02682</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2'129.55</t>
+          <t>9'515.00</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1032</v>
+        <v>0.0258</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.1188</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0726</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02682</t>
+          <t>CM-26-02549</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Muga Prado Enea Gran Reserva</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Bodegas Muga</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>234</v>
+        <v>1890</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>9'515.00</t>
+          <t>1'886.06</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0156</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1188</v>
+        <v>0.0236</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.063</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02549</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Muga Prado Enea Gran Reserva</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Muga</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1890</v>
+        <v>53</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>1'886.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0236</v>
+        <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02676</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -3256,26 +3016,22 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>0</v>
@@ -3300,124 +3056,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02605</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>168</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>146</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02695</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N16"/>
+  <autoFilter ref="A3:N14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3432,7 +3072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N163"/>
+  <dimension ref="A1:N164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3461,7 +3101,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-23 08:44  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5463,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-02745</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -5833,48 +5473,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>23'619.73</t>
+          <t>22'313.07</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.1986</v>
+        <v>0.2142</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.295</v>
+        <v>0.2786</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.2372</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -5883,58 +5523,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02464</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>475</v>
+        <v>181</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>44'390.76</t>
+          <t>23'619.73</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.0252</v>
+        <v>0.1986</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.5543</v>
+        <v>0.295</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.2368</v>
+        <v>0.2372</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -5943,58 +5583,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02348</t>
+          <t>CM-26-02464</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>34</v>
+        <v>475</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>1'650.84</t>
+          <t>44'390.76</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.3527</v>
+        <v>0.0252</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.0206</v>
+        <v>0.5543</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.2199</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6003,58 +5643,58 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02476</t>
+          <t>CM-26-02348</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Finca El Bosque</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Viñedos y Bodegas Sierra Cantabria</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1003</v>
+        <v>34</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>5.88%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>32'358.75</t>
+          <t>1'650.84</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.096</v>
+        <v>0.3527</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.4041</v>
+        <v>0.0206</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2192</v>
+        <v>0.2199</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6063,58 +5703,58 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03276</t>
+          <t>CM-26-02476</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Giaconda</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>76</v>
+        <v>1003</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>5'768.84</t>
+          <t>32'358.75</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.096</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.4041</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.2181</v>
+        <v>0.2192</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6123,58 +5763,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00648</t>
+          <t>CM-25-03276</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Criots Batard Montrachet Haute Densité</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Hubert Lamy</t>
+          <t>Giaconda</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>11'788.88</t>
+          <t>5'768.84</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.2609</v>
+        <v>0.3155</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.1472</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.2154</v>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6183,58 +5823,58 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02022</t>
+          <t>CM-26-00648</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Kayli Morgan Vineyard</t>
+          <t>Criots Batard Montrachet Haute Densité</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Hundred Acre</t>
+          <t>Hubert Lamy</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>6'911.52</t>
+          <t>11'788.88</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.2999</v>
+        <v>0.2609</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0863</v>
+        <v>0.1472</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.2145</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -6243,7 +5883,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00774</t>
+          <t>CM-26-02022</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -6253,48 +5893,48 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>La Grande Rue</t>
+          <t>Kayli Morgan Vineyard</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Domaine Francois Lamarche</t>
+          <t>Hundred Acre</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>12'881.25</t>
+          <t>6'911.52</t>
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.2999</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>0.1609</v>
+        <v>0.0863</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>0.2144</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -6303,7 +5943,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00010</t>
+          <t>CM-26-00774</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -6313,48 +5953,48 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>La Grande Rue</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Francois Lamarche</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>17'002.84</t>
+          <t>12'881.25</t>
         </is>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.2154</v>
+        <v>0.2501</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.2123</v>
+        <v>0.1609</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.2144</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -6363,58 +6003,58 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00553</t>
+          <t>CM-26-00010</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>37'269.73</t>
+          <t>17'002.84</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0.036</v>
+        <v>0.2154</v>
       </c>
       <c r="M51" s="6" t="n">
-        <v>0.4654</v>
+        <v>0.2123</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>0.2078</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -6423,58 +6063,58 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01142</t>
+          <t>CM-26-00553</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc de Margaux</t>
+          <t>DRC Assortment Case 10 Bottles (2LT, 1RI, 2RSV, 1GE, 2EC, 1CO, 1CC)</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>9'698.33</t>
+          <t>37'269.73</t>
         </is>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.2609</v>
+        <v>0.036</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.1211</v>
+        <v>0.4654</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.205</v>
+        <v>0.2078</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -6483,58 +6123,58 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-26-01142</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Pavillon Blanc de Margaux</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>9'339.37</t>
+          <t>9'698.33</t>
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>0.2555</v>
+        <v>0.2609</v>
       </c>
       <c r="M53" s="6" t="n">
-        <v>0.1166</v>
+        <v>0.1211</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>0.1999</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -6543,58 +6183,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>245</v>
+        <v>47</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>12'664.03</t>
+          <t>9'339.37</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.2202</v>
+        <v>0.2555</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.1581</v>
+        <v>0.1166</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1954</v>
+        <v>0.1999</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -6603,58 +6243,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>12'664.03</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.201</v>
+        <v>0.2202</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1822</v>
+        <v>0.1581</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1935</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -6663,58 +6303,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00844</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>10'560.34</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.222</v>
+        <v>0.201</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.1319</v>
+        <v>0.1822</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.186</v>
+        <v>0.1935</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -6723,58 +6363,58 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01486</t>
+          <t>CM-26-00844</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>3'550.60</t>
+          <t>10'560.34</t>
         </is>
       </c>
       <c r="L57" s="6" t="n">
-        <v>0.2729</v>
+        <v>0.222</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>0.0443</v>
+        <v>0.1319</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>0.1815</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -6783,58 +6423,58 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02108</t>
+          <t>CM-26-01486</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>21'336.21</t>
+          <t>3'496.43</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.12</v>
+        <v>0.2729</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.2664</v>
+        <v>0.0437</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.1786</v>
+        <v>0.1812</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
@@ -6843,7 +6483,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-02108</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -6853,48 +6493,48 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>21'336.21</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>0.1464</v>
+        <v>0.12</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>0.2217</v>
+        <v>0.2664</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>0.1765</v>
+        <v>0.1786</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -6903,58 +6543,58 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02475</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1015</v>
+        <v>41</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>25'984.56</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1464</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.3245</v>
+        <v>0.2217</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.1759</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -7203,58 +6843,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-02475</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>95</v>
+        <v>1015</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>16'003.16</t>
+          <t>23'950.56</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.1266</v>
+        <v>0.0708</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.1998</v>
+        <v>0.2991</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.1559</v>
+        <v>0.1621</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7263,58 +6903,58 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>1'277.97</t>
+          <t>16'003.16</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.2466</v>
+        <v>0.1266</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.016</v>
+        <v>0.1998</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.1544</v>
+        <v>0.1559</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7323,7 +6963,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -7333,7 +6973,7 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -7343,38 +6983,38 @@
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine Henri Gouges</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.222</v>
+        <v>0.2466</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.0412</v>
+        <v>0.016</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.1497</v>
+        <v>0.1544</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7383,58 +7023,58 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Henri Gouges</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.0462</v>
+        <v>0.222</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.3023</v>
+        <v>0.0412</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.1486</v>
+        <v>0.1497</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -7443,58 +7083,58 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2'246.57</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0.2244</v>
+        <v>0.0462</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.0281</v>
+        <v>0.3023</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.1459</v>
+        <v>0.1486</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -7503,58 +7143,58 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>2'246.57</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.1362</v>
+        <v>0.2244</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.1596</v>
+        <v>0.0281</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.1456</v>
+        <v>0.1459</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -7563,58 +7203,58 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02465</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>248</v>
+        <v>88</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>25'407.38</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0.024</v>
+        <v>0.1362</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0.3173</v>
+        <v>0.1596</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0.1413</v>
+        <v>0.1456</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -7623,58 +7263,58 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02409</t>
+          <t>CM-26-02465</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Tenuta Nuova</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Casanova di Neri</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>380</v>
+        <v>248</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>12'911.34</t>
+          <t>25'407.38</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.024</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.1612</v>
+        <v>0.3173</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.1404</v>
+        <v>0.1413</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -7683,58 +7323,58 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-02409</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>Brunello di Montalcino Tenuta Nuova</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Casanova di Neri</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>28</v>
+        <v>380</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>1'616.38</t>
+          <t>12'911.34</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.1266</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0.0202</v>
+        <v>0.1612</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.1366</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -7743,7 +7383,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02226</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -7753,48 +7393,48 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>9'090.00</t>
+          <t>18'434.16</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.1398</v>
+        <v>0.078</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.1135</v>
+        <v>0.2302</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.1293</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -7803,58 +7443,58 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02674</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Hosanna</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Château Hosanna</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>3'813.96</t>
+          <t>1'616.38</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0.1764</v>
+        <v>0.2142</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0.0476</v>
+        <v>0.0202</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.1249</v>
+        <v>0.1366</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -7863,7 +7503,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-02226</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -7873,48 +7513,48 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>313</v>
+        <v>43</v>
       </c>
       <c r="I76" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>9'090.00</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.0192</v>
+        <v>0.1398</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.282</v>
+        <v>0.1135</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.1243</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -7923,58 +7563,58 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01284</t>
+          <t>CM-26-02674</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Hosanna</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Château Hosanna</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>8'112.00</t>
+          <t>3'813.96</t>
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0.1332</v>
+        <v>0.1764</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>0.1013</v>
+        <v>0.0476</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>0.1204</v>
+        <v>0.1249</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -7983,58 +7623,58 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02474</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Mazoyères-Chambertin</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Arnaud Mortet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>9'311.67</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.12</v>
+        <v>0.0192</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.1163</v>
+        <v>0.282</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.1185</v>
+        <v>0.1243</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -8043,58 +7683,58 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00963</t>
+          <t>CM-26-01284</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>12'828.11</t>
+          <t>8'112.00</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>0.081</v>
+        <v>0.1332</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0.1602</v>
+        <v>0.1013</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0.1127</v>
+        <v>0.1204</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -8103,58 +7743,58 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00779</t>
+          <t>CM-25-02474</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Mazoyères-Chambertin</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Arnaud Mortet</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>10'707.33</t>
+          <t>9'311.67</t>
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.0936</v>
+        <v>0.12</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.1337</v>
+        <v>0.1163</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.1096</v>
+        <v>0.1185</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -8163,7 +7803,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02151</t>
+          <t>CM-26-00963</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -8173,48 +7813,48 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>La Romanée</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>11'000.00</t>
+          <t>12'828.11</t>
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.081</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>0.1374</v>
+        <v>0.1602</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>0.1079</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -8223,58 +7863,58 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02628</t>
+          <t>CM-26-00779</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Grillet Blanc</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Château Grillet</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>6'957.56</t>
+          <t>10'707.33</t>
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.1218</v>
+        <v>0.0936</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.1078</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -8283,7 +7923,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01423</t>
+          <t>CM-26-02151</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -8293,48 +7933,48 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Meursault Blanc</t>
+          <t>La Romanée</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine Coche-Dury</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>11'135.73</t>
+          <t>11'000.00</t>
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0882</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>0.1391</v>
+        <v>0.1374</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>0.1064</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -8343,7 +7983,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00967</t>
+          <t>CM-25-02628</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -8353,7 +7993,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger</t>
+          <t>Grillet Blanc</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -8363,38 +8003,38 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Grillet</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>317</v>
+        <v>197</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>12'111.33</t>
+          <t>6'957.56</t>
         </is>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.0756</v>
+        <v>0.1218</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.1512</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.1058</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -8403,7 +8043,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00772</t>
+          <t>CM-26-01423</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -8413,48 +8053,48 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Meursault Blanc</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine Coche-Dury</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>10'109.38</t>
+          <t>11'135.73</t>
         </is>
       </c>
       <c r="L85" s="6" t="n">
-        <v>0.0912</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="M85" s="6" t="n">
-        <v>0.1262</v>
+        <v>0.1391</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>0.1052</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -8463,58 +8103,58 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01249</t>
+          <t>CM-26-00967</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Pape Clément Blanc</t>
+          <t>Riesling Auslese Scharzhofberger</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Château Pape Clément</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>5'760.55</t>
+          <t>12'111.33</t>
         </is>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.0756</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.1512</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.1047</v>
+        <v>0.1058</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -8523,58 +8163,58 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01320</t>
+          <t>CM-26-00772</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>4'696.54</t>
+          <t>10'109.38</t>
         </is>
       </c>
       <c r="L87" s="6" t="n">
-        <v>0.132</v>
+        <v>0.0912</v>
       </c>
       <c r="M87" s="6" t="n">
-        <v>0.0586</v>
+        <v>0.1262</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>0.1026</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -8583,58 +8223,58 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01550</t>
+          <t>CM-26-01249</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Pape Clément Blanc</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Château Pape Clément</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="I88" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>8'407.01</t>
+          <t>5'760.55</t>
         </is>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.099</v>
+        <v>0.1266</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.105</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>0.1014</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -8643,58 +8283,58 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01376</t>
+          <t>CM-26-01320</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Vieilles Vignes Françaises</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>Bollinger</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>348</v>
+        <v>91</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>13'791.85</t>
+          <t>4'696.54</t>
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>0.0516</v>
+        <v>0.132</v>
       </c>
       <c r="M89" s="6" t="n">
-        <v>0.1722</v>
+        <v>0.0586</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>0.0998</v>
+        <v>0.1026</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -8703,58 +8343,58 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02291</t>
+          <t>CM-26-01550</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>440</v>
+        <v>121</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>18'010.29</t>
+          <t>8'407.01</t>
         </is>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0.0138</v>
+        <v>0.099</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>0.2249</v>
+        <v>0.105</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>0.0982</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -8763,58 +8403,58 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02232</t>
+          <t>CM-26-01376</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Léoville Las Cases</t>
+          <t>Champagne Brut Vieilles Vignes Françaises</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Bollinger</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>11'683.71</t>
+          <t>13'791.85</t>
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0516</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>0.1459</v>
+        <v>0.1722</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>0.0969</v>
+        <v>0.0998</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -8823,58 +8463,58 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01542</t>
+          <t>CM-26-02291</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>87</v>
+        <v>440</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2'424.17</t>
+          <t>18'010.29</t>
         </is>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0138</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>0.0303</v>
+        <v>0.2249</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>0.0949</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -8883,22 +8523,22 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00958</t>
+          <t>CM-26-02232</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -8908,33 +8548,33 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>487</v>
+        <v>281</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>14'454.90</t>
+          <t>11'683.71</t>
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>0.1805</v>
+        <v>0.1459</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>0.0945</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -8943,58 +8583,58 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01262</t>
+          <t>CM-26-01542</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>235</v>
+        <v>87</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>2'724.45</t>
+          <t>2'424.17</t>
         </is>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.1278</v>
+        <v>0.138</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.034</v>
+        <v>0.0303</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -9003,7 +8643,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-00958</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -9013,48 +8653,48 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Assortment Léoville Las Cases Grape Varieties 6x75cl (2x LLC, 1x Cabernet Sauvignon, 1x Merlot, 1x Cabernet Franc, 1x Petit Verdot)</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>68</v>
+        <v>487</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>7'370.74</t>
+          <t>14'454.90</t>
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0372</v>
       </c>
       <c r="M95" s="6" t="n">
-        <v>0.092</v>
+        <v>0.1805</v>
       </c>
       <c r="N95" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -9063,58 +8703,58 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02618</t>
+          <t>CM-26-01262</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>11'370.00</t>
+          <t>2'724.45</t>
         </is>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.1278</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.142</v>
+        <v>0.034</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.0834</v>
+        <v>0.09030000000000001</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -9123,58 +8763,58 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02357</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2'869.98</t>
+          <t>7'370.74</t>
         </is>
       </c>
       <c r="L97" s="6" t="n">
-        <v>0.1146</v>
+        <v>0.0882</v>
       </c>
       <c r="M97" s="6" t="n">
-        <v>0.0358</v>
+        <v>0.092</v>
       </c>
       <c r="N97" s="6" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -9183,58 +8823,58 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-02357</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>La Nieta</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Viñedos de Páganos</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>476</v>
+        <v>157</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>2'869.98</t>
         </is>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.0504</v>
+        <v>0.1146</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.1317</v>
+        <v>0.0358</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.0829</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -9243,58 +8883,58 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>68</v>
+        <v>476</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>5'945.00</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.0504</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>0.0742</v>
+        <v>0.1317</v>
       </c>
       <c r="N99" s="6" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -9303,7 +8943,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -9313,48 +8953,48 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>5'945.00</t>
         </is>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0882</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.1359</v>
+        <v>0.0742</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.0814</v>
+        <v>0.08260000000000001</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -9363,17 +9003,17 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02514</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -9383,38 +9023,38 @@
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Veuve Clicquot Ponsardin</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>66</v>
+        <v>268</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>4'283.11</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>0.0912</v>
+        <v>0.045</v>
       </c>
       <c r="M101" s="6" t="n">
-        <v>0.0535</v>
+        <v>0.1359</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>0.0761</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -9423,58 +9063,58 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-02514</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Veuve Clicquot Ponsardin</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>2'129.55</t>
+          <t>4'283.11</t>
         </is>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.1032</v>
+        <v>0.0912</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.0266</v>
+        <v>0.0535</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.0726</v>
+        <v>0.0761</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -9483,58 +9123,58 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I103" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>697.16</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L103" s="6" t="n">
-        <v>0.1134</v>
+        <v>0.1032</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0266</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -9543,7 +9183,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -9553,48 +9193,48 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>697.16</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.1134</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -9603,58 +9243,58 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02158</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Prieuré Roch</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>11'314.66</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0774</v>
       </c>
       <c r="M105" s="6" t="n">
-        <v>0.1413</v>
+        <v>0.0625</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>0.0698</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -9663,17 +9303,17 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02370</t>
+          <t>CM-26-02618</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -9683,38 +9323,38 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>54</v>
+        <v>278</v>
       </c>
       <c r="I106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>611.10</t>
+          <t>11'370.00</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.111</v>
+        <v>0.0216</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.0076</v>
+        <v>0.142</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.0696</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -9723,27 +9363,27 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02154</t>
+          <t>CM-26-02158</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Morey St. Denis Clos de la Bussière</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine du Prieuré Roch</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -9752,29 +9392,29 @@
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>7'898.70</t>
+          <t>11'314.66</t>
         </is>
       </c>
       <c r="L107" s="6" t="n">
-        <v>0.0414</v>
+        <v>0.0222</v>
       </c>
       <c r="M107" s="6" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1413</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>0.0643</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -9783,58 +9423,58 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02682</t>
+          <t>CM-26-02370</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Finca El Bosque</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Viñedos y Bodegas Sierra Cantabria</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H108" s="4" t="n">
-        <v>234</v>
+        <v>54</v>
       </c>
       <c r="I108" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>9'515.00</t>
+          <t>603.91</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.111</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.1188</v>
+        <v>0.0075</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.063</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -9843,7 +9483,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01755</t>
+          <t>CM-26-02154</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -9853,48 +9493,48 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Echézeaux</t>
+          <t>Morey St. Denis Clos de la Bussière</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>8'422.42</t>
+          <t>7'898.70</t>
         </is>
       </c>
       <c r="L109" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0414</v>
       </c>
       <c r="M109" s="6" t="n">
-        <v>0.1052</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="N109" s="6" t="n">
-        <v>0.0586</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -9903,58 +9543,58 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01481</t>
+          <t>CM-26-02682</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Ca' Marcanda</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Ca' Marcanda - Gaja</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H110" s="4" t="n">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>2'329.50</t>
+          <t>9'515.00</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.0291</v>
+        <v>0.1188</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>0.0545</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -9963,58 +9603,58 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01495</t>
+          <t>CM-26-01755</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Echézeaux</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
-        <v>393</v>
+        <v>216</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2'848.18</t>
+          <t>8'422.42</t>
         </is>
       </c>
       <c r="L111" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.0276</v>
       </c>
       <c r="M111" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.1052</v>
       </c>
       <c r="N111" s="6" t="n">
-        <v>0.051</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -10023,58 +9663,58 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01323</t>
+          <t>CM-26-01481</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Ca' Marcanda</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Ca' Marcanda - Gaja</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H112" s="4" t="n">
-        <v>100</v>
+        <v>252</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>2'520.00</t>
+          <t>2'329.50</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.06</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.0315</v>
+        <v>0.0291</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>0.0486</v>
+        <v>0.0545</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -10083,22 +9723,22 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01266</t>
+          <t>CM-26-01495</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Puligny Montrachet</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -10108,33 +9748,33 @@
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
-        <v>257</v>
+        <v>393</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>3'361.28</t>
+          <t>2'848.18</t>
         </is>
       </c>
       <c r="L113" s="6" t="n">
-        <v>0.0468</v>
+        <v>0.0612</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>0.042</v>
+        <v>0.0356</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>0.0449</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -10143,7 +9783,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02200</t>
+          <t>CM-26-01323</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -10153,48 +9793,48 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Charmes Chambertin V.V.</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Domaine Perrot Minot</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H114" s="4" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="I114" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>4'920.00</t>
+          <t>2'520.00</t>
         </is>
       </c>
       <c r="L114" s="4" t="n">
-        <v>0.0336</v>
+        <v>0.06</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>0.0614</v>
+        <v>0.0315</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -10203,7 +9843,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01265</t>
+          <t>CM-26-01266</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -10213,12 +9853,12 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Puligny Montrachet</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -10232,29 +9872,29 @@
         </is>
       </c>
       <c r="H115" s="6" t="n">
-        <v>323</v>
+        <v>257</v>
       </c>
       <c r="I115" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2'912.26</t>
+          <t>3'361.28</t>
         </is>
       </c>
       <c r="L115" s="6" t="n">
-        <v>0.0372</v>
+        <v>0.0468</v>
       </c>
       <c r="M115" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.042</v>
       </c>
       <c r="N115" s="6" t="n">
-        <v>0.0369</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -10263,58 +9903,58 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02358</t>
+          <t>CM-26-02200</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Charmes Chambertin V.V.</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Domaine Perrot Minot</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H116" s="4" t="n">
-        <v>1308</v>
+        <v>177</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>3'555.07</t>
+          <t>4'920.00</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.0276</v>
+        <v>0.0336</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.0444</v>
+        <v>0.0614</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>0.0343</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -10323,58 +9963,58 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00851</t>
+          <t>CM-26-01265</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>4'180.96</t>
+          <t>2'912.26</t>
         </is>
       </c>
       <c r="L117" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.0372</v>
       </c>
       <c r="M117" s="6" t="n">
-        <v>0.0522</v>
+        <v>0.0364</v>
       </c>
       <c r="N117" s="6" t="n">
-        <v>0.0342</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -10383,7 +10023,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02656</t>
+          <t>CM-26-02358</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -10393,48 +10033,48 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
+          <t>La Nieta</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Weingut Markus Molitor</t>
+          <t>Viñedos de Páganos</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H118" s="4" t="n">
-        <v>324</v>
+        <v>1308</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>1'893.50</t>
+          <t>3'555.07</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0276</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>0.0236</v>
+        <v>0.0444</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>0.0318</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -10443,58 +10083,58 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02227</t>
+          <t>CM-26-00851</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Clos de Tart</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
-        <v>478</v>
+        <v>271</v>
       </c>
       <c r="I119" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>3'879.31</t>
+          <t>4'180.96</t>
         </is>
       </c>
       <c r="L119" s="6" t="n">
-        <v>0.0126</v>
+        <v>0.0222</v>
       </c>
       <c r="M119" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.0522</v>
       </c>
       <c r="N119" s="6" t="n">
-        <v>0.0269</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
@@ -10503,58 +10143,58 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02549</t>
+          <t>CM-25-02656</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Muga Prado Enea Gran Reserva</t>
+          <t>Riesling  Zeltinger Sonnenuhr Beerenauslese Goldkapsel</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Muga</t>
+          <t>Weingut Markus Molitor</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="H120" s="4" t="n">
-        <v>1890</v>
+        <v>324</v>
       </c>
       <c r="I120" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>1'886.06</t>
+          <t>1'893.50</t>
         </is>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.0156</v>
+        <v>0.0372</v>
       </c>
       <c r="M120" s="4" t="n">
         <v>0.0236</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
@@ -10563,58 +10203,58 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01268</t>
+          <t>CM-26-02227</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
-        <v>280</v>
+        <v>478</v>
       </c>
       <c r="I121" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>568.18</t>
+          <t>3'879.31</t>
         </is>
       </c>
       <c r="L121" s="6" t="n">
-        <v>0.0216</v>
+        <v>0.0126</v>
       </c>
       <c r="M121" s="6" t="n">
-        <v>0.0071</v>
+        <v>0.0484</v>
       </c>
       <c r="N121" s="6" t="n">
-        <v>0.0158</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
@@ -10623,58 +10263,58 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01497</t>
+          <t>CM-26-02549</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Meursault Crotots</t>
+          <t>Muga Prado Enea Gran Reserva</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Bodegas Muga</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H122" s="4" t="n">
-        <v>483</v>
+        <v>1890</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>968.26</t>
+          <t>1'886.06</t>
         </is>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.0126</v>
+        <v>0.0156</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.0121</v>
+        <v>0.0236</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
@@ -10683,58 +10323,58 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-26-01268</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Savigny les Beaune 1er Cru Aux Vergelesses</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H123" s="6" t="n">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>568.18</t>
         </is>
       </c>
       <c r="L123" s="6" t="n">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="M123" s="6" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="N123" s="6" t="n">
-        <v>0</v>
+        <v>0.0158</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
@@ -10743,58 +10383,58 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-01497</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Meursault Crotots</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H124" s="4" t="n">
-        <v>42</v>
+        <v>483</v>
       </c>
       <c r="I124" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>968.26</t>
         </is>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0</v>
+        <v>0.0121</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>0</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
@@ -10803,36 +10443,36 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02676</t>
+          <t>CM-26-01981</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Kayli Morgan Vineyard</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Hundred Acre</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="I125" s="6" t="n">
         <v>0</v>
@@ -10863,7 +10503,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -10873,26 +10513,26 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H126" s="4" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I126" s="4" t="n">
         <v>0</v>
@@ -10923,7 +10563,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02438</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -10933,26 +10573,26 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée Conti</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
-        <v>410</v>
+        <v>53</v>
       </c>
       <c r="I127" s="6" t="n">
         <v>0</v>
@@ -10983,36 +10623,36 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01614</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H128" s="4" t="n">
-        <v>36</v>
+        <v>613</v>
       </c>
       <c r="I128" s="4" t="n">
         <v>0</v>
@@ -11043,7 +10683,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -11053,26 +10693,26 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H129" s="6" t="n">
-        <v>643</v>
+        <v>26</v>
       </c>
       <c r="I129" s="6" t="n">
         <v>0</v>
@@ -11103,7 +10743,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02605</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -11113,22 +10753,26 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr"/>
+          <t>DRC Corton Charlemagne</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H130" s="4" t="n">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="I130" s="4" t="n">
         <v>0</v>
@@ -11159,36 +10803,36 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="I131" s="6" t="n">
         <v>0</v>
@@ -11219,7 +10863,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01508</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -11229,26 +10873,26 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H132" s="4" t="n">
-        <v>30</v>
+        <v>643</v>
       </c>
       <c r="I132" s="4" t="n">
         <v>0</v>
@@ -11279,36 +10923,36 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01513</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I133" s="6" t="n">
         <v>0</v>
@@ -11339,7 +10983,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-26-02220</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -11349,26 +10993,26 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H134" s="4" t="n">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="I134" s="4" t="n">
         <v>0</v>
@@ -11399,7 +11043,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -11409,26 +11053,26 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H135" s="6" t="n">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="I135" s="6" t="n">
         <v>0</v>
@@ -11459,7 +11103,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01614</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -11469,26 +11113,26 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H136" s="4" t="n">
-        <v>613</v>
+        <v>30</v>
       </c>
       <c r="I136" s="4" t="n">
         <v>0</v>
@@ -11519,36 +11163,36 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01513</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H137" s="6" t="n">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="I137" s="6" t="n">
         <v>0</v>
@@ -11579,36 +11223,36 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H138" s="4" t="n">
-        <v>86</v>
+        <v>716</v>
       </c>
       <c r="I138" s="4" t="n">
         <v>0</v>
@@ -11699,7 +11343,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01512</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -11714,21 +11358,21 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H140" s="4" t="n">
-        <v>716</v>
+        <v>20</v>
       </c>
       <c r="I140" s="4" t="n">
         <v>0</v>
@@ -11759,7 +11403,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -11769,26 +11413,26 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I141" s="6" t="n">
         <v>0</v>
@@ -11819,36 +11463,36 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02073</t>
+          <t>CM-25-02438</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>DRC Romanée Conti</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H142" s="4" t="n">
-        <v>223</v>
+        <v>410</v>
       </c>
       <c r="I142" s="4" t="n">
         <v>0</v>
@@ -11879,7 +11523,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -11889,12 +11533,12 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
@@ -11904,11 +11548,11 @@
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I143" s="6" t="n">
         <v>0</v>
@@ -11939,7 +11583,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -11949,12 +11593,12 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -11964,11 +11608,11 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H144" s="4" t="n">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="I144" s="4" t="n">
         <v>0</v>
@@ -11999,7 +11643,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -12009,26 +11653,26 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H145" s="6" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I145" s="6" t="n">
         <v>0</v>
@@ -12059,7 +11703,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -12069,17 +11713,17 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -12088,7 +11732,7 @@
         </is>
       </c>
       <c r="H146" s="4" t="n">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="I146" s="4" t="n">
         <v>0</v>
@@ -12119,7 +11763,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02220</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -12129,26 +11773,26 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="I147" s="6" t="n">
         <v>0</v>
@@ -12179,7 +11823,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-02406</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -12189,26 +11833,26 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H148" s="4" t="n">
-        <v>63</v>
+        <v>775</v>
       </c>
       <c r="I148" s="4" t="n">
         <v>0</v>
@@ -12239,7 +11883,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02695</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -12249,26 +11893,26 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H149" s="6" t="n">
-        <v>77</v>
+        <v>543</v>
       </c>
       <c r="I149" s="6" t="n">
         <v>0</v>
@@ -12299,7 +11943,7 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01512</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -12309,7 +11953,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -12324,11 +11968,11 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H150" s="4" t="n">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="I150" s="4" t="n">
         <v>0</v>
@@ -12359,7 +12003,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02463</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -12369,26 +12013,26 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="I151" s="6" t="n">
         <v>0</v>
@@ -12419,7 +12063,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-02463</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -12429,26 +12073,26 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H152" s="4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I152" s="4" t="n">
         <v>0</v>
@@ -12479,7 +12123,7 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02062</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -12489,26 +12133,26 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I153" s="6" t="n">
         <v>0</v>
@@ -12539,7 +12183,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -12549,26 +12193,26 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
-        <v>543</v>
+        <v>362</v>
       </c>
       <c r="I154" s="4" t="n">
         <v>0</v>
@@ -12599,36 +12243,36 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01981</t>
+          <t>CM-26-02062</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Kayli Morgan Vineyard</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>Hundred Acre</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="I155" s="6" t="n">
         <v>0</v>
@@ -12659,36 +12303,36 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H156" s="4" t="n">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="I156" s="4" t="n">
         <v>0</v>
@@ -12719,7 +12363,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -12729,26 +12373,26 @@
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H157" s="6" t="n">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="I157" s="6" t="n">
         <v>0</v>
@@ -12779,7 +12423,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01680</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -12789,26 +12433,26 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H158" s="4" t="n">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="I158" s="4" t="n">
         <v>0</v>
@@ -12839,36 +12483,36 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-02073</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H159" s="6" t="n">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="I159" s="6" t="n">
         <v>0</v>
@@ -12899,7 +12543,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02406</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -12909,26 +12553,26 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H160" s="4" t="n">
-        <v>775</v>
+        <v>63</v>
       </c>
       <c r="I160" s="4" t="n">
         <v>0</v>
@@ -12959,36 +12603,36 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H161" s="6" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I161" s="6" t="n">
         <v>0</v>
@@ -13019,7 +12663,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -13029,26 +12673,26 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H162" s="4" t="n">
-        <v>362</v>
+        <v>103</v>
       </c>
       <c r="I162" s="4" t="n">
         <v>0</v>
@@ -13079,36 +12723,32 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr"/>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H163" s="6" t="n">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="I163" s="6" t="n">
         <v>0</v>
@@ -13133,8 +12773,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>CM-26-01680</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>DRC Richebourg</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>Domaine de la Romanée Conti</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="n">
+        <v>239</v>
+      </c>
+      <c r="I164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:N163"/>
+  <autoFilter ref="A3:N164"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-01 08:26  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -1905,17 +1905,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>34'041.76</t>
+          <t>33'975.19</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.2801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.4251</v>
+        <v>0.4243</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.3381</v>
+        <v>0.3378</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 22 Sep 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 24 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-01 08:26  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -2266,17 +2266,17 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>22'313.07</t>
+          <t>21'612.82</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
         <v>0.2142</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.2786</v>
+        <v>0.2699</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.24</v>
+        <v>0.2365</v>
       </c>
     </row>
   </sheetData>
@@ -2295,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2317,14 +2317,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 30 Aug 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 01 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-01 08:26  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -2567,26 +2567,26 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>22'313.07</t>
+          <t>21'612.82</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>0.2142</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2786</v>
+        <v>0.2699</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.24</v>
+        <v>0.2365</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02695</t>
+          <t>CM-26-02618</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2611,213 +2611,213 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>18'434.16</t>
+          <t>32'880.03</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.078</v>
+        <v>0.0432</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2302</v>
+        <v>0.4106</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1389</v>
+        <v>0.1902</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02674</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Hosanna</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Hosanna</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>3'813.96</t>
+          <t>18'434.16</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1764</v>
+        <v>0.078</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0476</v>
+        <v>0.2302</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1249</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-02674</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Hosanna</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Château Hosanna</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2'129.55</t>
+          <t>3'813.96</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1032</v>
+        <v>0.1764</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0476</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0726</v>
+        <v>0.1249</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02618</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>278</v>
+        <v>58</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>11'370.00</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.1032</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.142</v>
+        <v>0.0266</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0698</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2882,71 +2882,71 @@
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02549</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Muga Prado Enea Gran Reserva</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Muga</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1890</v>
+        <v>53</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>1'886.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0236</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02676</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -2956,26 +2956,22 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr"/>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
@@ -3000,64 +2996,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02605</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N14"/>
+  <autoFilter ref="A3:N13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3101,7 +3041,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-29 08:22  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-01 08:26  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4484,17 +4424,17 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>34'041.76</t>
+          <t>33'975.19</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.2801</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.4251</v>
+        <v>0.4243</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.3381</v>
+        <v>0.3378</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -5463,7 +5403,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02745</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -5473,48 +5413,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>22'313.07</t>
+          <t>23'619.73</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.1986</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.2786</v>
+        <v>0.295</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.24</v>
+        <v>0.2372</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -5523,58 +5463,58 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-02464</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>181</v>
+        <v>475</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>23'619.73</t>
+          <t>44'390.76</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1986</v>
+        <v>0.0252</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.295</v>
+        <v>0.5543</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.2372</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -5583,58 +5523,58 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02464</t>
+          <t>CM-26-02745</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>44'390.76</t>
+          <t>21'612.82</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.0252</v>
+        <v>0.2142</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.5543</v>
+        <v>0.2699</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.2368</v>
+        <v>0.2365</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -5744,17 +5684,17 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>32'358.75</t>
+          <t>32'308.45</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
         <v>0.096</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4041</v>
+        <v>0.4035</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.2192</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6183,58 +6123,58 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00579</t>
+          <t>CM-25-03240</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Musigny Vieilles Vignes</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Domaine Comte Georges de Vogüe</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>47</v>
+        <v>245</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>3.67%</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>9'339.37</t>
+          <t>12'664.03</t>
         </is>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.2555</v>
+        <v>0.2202</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.1166</v>
+        <v>0.1581</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1999</v>
+        <v>0.1954</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -6243,58 +6183,58 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03240</t>
+          <t>CM-26-01239</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Eisele Vineyard</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>12'664.03</t>
+          <t>14'592.69</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0.2202</v>
+        <v>0.201</v>
       </c>
       <c r="M55" s="6" t="n">
-        <v>0.1581</v>
+        <v>0.1822</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>0.1954</v>
+        <v>0.1935</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -6303,58 +6243,58 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01239</t>
+          <t>CM-26-02618</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Eisele Vineyard</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>14'592.69</t>
+          <t>32'880.03</t>
         </is>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.201</v>
+        <v>0.0432</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.1822</v>
+        <v>0.4106</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1935</v>
+        <v>0.1902</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -8763,7 +8703,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-00579</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -8773,48 +8713,48 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Musigny Vieilles Vignes</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Comte Georges de Vogüe</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I97" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>7'370.74</t>
+          <t>2'715.37</t>
         </is>
       </c>
       <c r="L97" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.1278</v>
       </c>
       <c r="M97" s="6" t="n">
-        <v>0.092</v>
+        <v>0.0339</v>
       </c>
       <c r="N97" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.0902</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -8823,58 +8763,58 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02357</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>2'869.98</t>
+          <t>7'370.74</t>
         </is>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.1146</v>
+        <v>0.0882</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.0358</v>
+        <v>0.092</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -8883,58 +8823,58 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-02357</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>La Nieta</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Viñedos de Páganos</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>476</v>
+        <v>157</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>2'869.98</t>
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.1146</v>
       </c>
       <c r="M99" s="6" t="n">
-        <v>0.1317</v>
+        <v>0.0358</v>
       </c>
       <c r="N99" s="6" t="n">
-        <v>0.0829</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -8943,58 +8883,58 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H100" s="4" t="n">
-        <v>68</v>
+        <v>476</v>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>5'945.00</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.0504</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.0742</v>
+        <v>0.1317</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -9003,7 +8943,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -9013,48 +8953,48 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>5'945.00</t>
         </is>
       </c>
       <c r="L101" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0882</v>
       </c>
       <c r="M101" s="6" t="n">
-        <v>0.1359</v>
+        <v>0.0742</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>0.0814</v>
+        <v>0.08260000000000001</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -9063,17 +9003,17 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02514</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -9083,38 +9023,38 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Veuve Clicquot Ponsardin</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H102" s="4" t="n">
-        <v>66</v>
+        <v>268</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>4'283.11</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.045</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.0535</v>
+        <v>0.1359</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -9123,58 +9063,58 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-02514</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Veuve Clicquot Ponsardin</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I103" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2'129.55</t>
+          <t>4'283.11</t>
         </is>
       </c>
       <c r="L103" s="6" t="n">
-        <v>0.1032</v>
+        <v>0.0912</v>
       </c>
       <c r="M103" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0535</v>
       </c>
       <c r="N103" s="6" t="n">
-        <v>0.0726</v>
+        <v>0.0761</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -9183,58 +9123,58 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I104" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>697.16</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.1134</v>
+        <v>0.1032</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0266</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -9243,7 +9183,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -9253,48 +9193,48 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>697.16</t>
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.1134</v>
       </c>
       <c r="M105" s="6" t="n">
-        <v>0.0625</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -9303,58 +9243,58 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02618</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>11'370.00</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0774</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.142</v>
+        <v>0.0625</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.0698</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -10443,36 +10383,36 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01981</t>
+          <t>CM-26-00728</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Kayli Morgan Vineyard</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>Hundred Acre</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="I125" s="6" t="n">
         <v>0</v>
@@ -10503,7 +10443,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -10513,26 +10453,26 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H126" s="4" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="I126" s="4" t="n">
         <v>0</v>
@@ -10563,7 +10503,7 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02676</t>
+          <t>CM-26-01156</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -10573,26 +10513,26 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="I127" s="6" t="n">
         <v>0</v>
@@ -10623,7 +10563,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01614</t>
+          <t>CM-26-01155</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -10633,26 +10573,26 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H128" s="4" t="n">
-        <v>613</v>
+        <v>103</v>
       </c>
       <c r="I128" s="4" t="n">
         <v>0</v>
@@ -10683,7 +10623,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01038</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -10693,26 +10633,26 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H129" s="6" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="I129" s="6" t="n">
         <v>0</v>
@@ -10743,7 +10683,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-00874</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -10753,26 +10693,26 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Leoville Las Cases (Ex-Château)</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H130" s="4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I130" s="4" t="n">
         <v>0</v>
@@ -10803,36 +10743,36 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-26-00854</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Clos de Tart (Ex Domaine)</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Mommessin</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
-        <v>91</v>
+        <v>543</v>
       </c>
       <c r="I131" s="6" t="n">
         <v>0</v>
@@ -10863,7 +10803,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-26-00822</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -10873,26 +10813,26 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H132" s="4" t="n">
-        <v>643</v>
+        <v>92</v>
       </c>
       <c r="I132" s="4" t="n">
         <v>0</v>
@@ -10923,7 +10863,7 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-26-00813</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -10933,26 +10873,26 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>Pingus</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Dominio de Pingus</t>
         </is>
       </c>
       <c r="G133" s="6" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I133" s="6" t="n">
         <v>0</v>
@@ -10983,7 +10923,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02220</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -10993,26 +10933,26 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H134" s="4" t="n">
-        <v>10</v>
+        <v>362</v>
       </c>
       <c r="I134" s="4" t="n">
         <v>0</v>
@@ -11043,7 +10983,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -11053,26 +10993,26 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H135" s="6" t="n">
-        <v>252</v>
+        <v>129</v>
       </c>
       <c r="I135" s="6" t="n">
         <v>0</v>
@@ -11103,7 +11043,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01508</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -11113,26 +11053,26 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H136" s="4" t="n">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="I136" s="4" t="n">
         <v>0</v>
@@ -11163,36 +11103,36 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01513</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H137" s="6" t="n">
-        <v>22</v>
+        <v>252</v>
       </c>
       <c r="I137" s="6" t="n">
         <v>0</v>
@@ -11223,7 +11163,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -11233,26 +11173,26 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H138" s="4" t="n">
-        <v>716</v>
+        <v>42</v>
       </c>
       <c r="I138" s="4" t="n">
         <v>0</v>
@@ -11283,7 +11223,7 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -11293,26 +11233,26 @@
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H139" s="6" t="n">
-        <v>240</v>
+        <v>643</v>
       </c>
       <c r="I139" s="6" t="n">
         <v>0</v>
@@ -11343,7 +11283,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01512</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -11353,26 +11293,26 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H140" s="4" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="I140" s="4" t="n">
         <v>0</v>
@@ -11403,7 +11343,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -11413,26 +11353,26 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G141" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="I141" s="6" t="n">
         <v>0</v>
@@ -11463,7 +11403,7 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02438</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -11473,26 +11413,26 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée Conti</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H142" s="4" t="n">
-        <v>410</v>
+        <v>116</v>
       </c>
       <c r="I142" s="4" t="n">
         <v>0</v>
@@ -11523,7 +11463,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -11533,12 +11473,12 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
@@ -11548,11 +11488,11 @@
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I143" s="6" t="n">
         <v>0</v>
@@ -11583,7 +11523,7 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-02463</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -11593,12 +11533,12 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -11608,11 +11548,11 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H144" s="4" t="n">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="I144" s="4" t="n">
         <v>0</v>
@@ -11643,7 +11583,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00813</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -11653,26 +11593,26 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Pingus</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>Dominio de Pingus</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H145" s="6" t="n">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="I145" s="6" t="n">
         <v>0</v>
@@ -11703,7 +11643,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01156</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -11713,26 +11653,26 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H146" s="4" t="n">
-        <v>28</v>
+        <v>716</v>
       </c>
       <c r="I146" s="4" t="n">
         <v>0</v>
@@ -11763,7 +11703,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00822</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -11773,26 +11713,26 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="I147" s="6" t="n">
         <v>0</v>
@@ -11823,7 +11763,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02406</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -11833,26 +11773,22 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H148" s="4" t="n">
-        <v>775</v>
+        <v>168</v>
       </c>
       <c r="I148" s="4" t="n">
         <v>0</v>
@@ -11883,7 +11819,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00854</t>
+          <t>CM-26-02406</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -11893,7 +11829,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Clos de Tart (Ex Domaine)</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -11903,16 +11839,16 @@
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>Mommessin</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H149" s="6" t="n">
-        <v>543</v>
+        <v>775</v>
       </c>
       <c r="I149" s="6" t="n">
         <v>0</v>
@@ -11943,7 +11879,7 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-02220</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -11953,26 +11889,26 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H150" s="4" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="I150" s="4" t="n">
         <v>0</v>
@@ -12003,36 +11939,36 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00728</t>
+          <t>CM-26-02073</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="I151" s="6" t="n">
         <v>0</v>
@@ -12063,7 +11999,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02463</t>
+          <t>CM-26-02062</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -12073,26 +12009,26 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H152" s="4" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I152" s="4" t="n">
         <v>0</v>
@@ -12123,36 +12059,36 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00874</t>
+          <t>CM-26-01981</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Leoville Las Cases (Ex-Château)</t>
+          <t>Kayli Morgan Vineyard</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Hundred Acre</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="I153" s="6" t="n">
         <v>0</v>
@@ -12183,7 +12119,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-01680</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -12193,12 +12129,12 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -12208,11 +12144,11 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
-        <v>362</v>
+        <v>239</v>
       </c>
       <c r="I154" s="4" t="n">
         <v>0</v>
@@ -12243,7 +12179,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02062</t>
+          <t>CM-26-01614</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -12253,26 +12189,26 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
-        <v>47</v>
+        <v>613</v>
       </c>
       <c r="I155" s="6" t="n">
         <v>0</v>
@@ -12303,7 +12239,7 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01513</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -12328,11 +12264,11 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H156" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I156" s="4" t="n">
         <v>0</v>
@@ -12363,7 +12299,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01512</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -12388,11 +12324,11 @@
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H157" s="6" t="n">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="I157" s="6" t="n">
         <v>0</v>
@@ -12423,7 +12359,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -12433,26 +12369,26 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H158" s="4" t="n">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="I158" s="4" t="n">
         <v>0</v>
@@ -12483,36 +12419,36 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02073</t>
+          <t>CM-26-01482</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H159" s="6" t="n">
-        <v>223</v>
+        <v>36</v>
       </c>
       <c r="I159" s="6" t="n">
         <v>0</v>
@@ -12543,7 +12479,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01038</t>
+          <t>CM-26-01479</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -12553,26 +12489,26 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H160" s="4" t="n">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="I160" s="4" t="n">
         <v>0</v>
@@ -12603,36 +12539,36 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H161" s="6" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I161" s="6" t="n">
         <v>0</v>
@@ -12663,36 +12599,36 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01155</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H162" s="4" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="I162" s="4" t="n">
         <v>0</v>
@@ -12723,32 +12659,36 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02605</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr"/>
+          <t>Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H163" s="6" t="n">
-        <v>168</v>
+        <v>91</v>
       </c>
       <c r="I163" s="6" t="n">
         <v>0</v>
@@ -12779,7 +12719,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01680</t>
+          <t>CM-25-02438</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -12789,12 +12729,12 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>DRC Romanée Conti</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -12804,11 +12744,11 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H164" s="4" t="n">
-        <v>239</v>
+        <v>410</v>
       </c>
       <c r="I164" s="4" t="n">
         <v>0</v>

--- a/AVUwinnersCM/delayed_winners.xlsx
+++ b/AVUwinnersCM/delayed_winners.xlsx
@@ -14,9 +14,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 Delayed Winners'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 30 Days'!$A$3:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Delayed Campaigns'!$A$3:$N$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-15 14:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-19 09:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>12'825.56</t>
+          <t>10'413.56</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1602</v>
+        <v>0.13</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.6641</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>18'028.54</t>
+          <t>18'595.54</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
         <v>0.6977</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2251</v>
+        <v>0.2322</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5087</v>
+        <v>0.5115</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2114,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2136,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 08 Oct 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 7 Days (since 12 Oct 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-15 14:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-19 09:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2221,151 +2221,151 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02844</t>
+          <t>CM-26-02875</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Bâtard Montrachet</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château de la Maltroye</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>14.29%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>10'224.17</t>
+          <t>45'600.00</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.8572</v>
+        <v>0.066</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.5694</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.5654</v>
+        <v>0.2674</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02854</t>
+          <t>CM-26-02879</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Barolo Villero Riserva</t>
+          <t>Canta la Perdiz</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Vietti</t>
+          <t>Bodega Dominio del Aguila</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>11.63%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>18'028.54</t>
+          <t>7'140.00</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.6977</v>
+        <v>0.24</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2251</v>
+        <v>0.0892</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5087</v>
+        <v>0.1797</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02875</t>
+          <t>CM-26-02886</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Corton Charlemagne</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Albert Bichot</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -2374,187 +2374,187 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>45'600.00</t>
+          <t>3'533.01</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.066</v>
+        <v>0.2537</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5694</v>
+        <v>0.0441</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2674</v>
+        <v>0.1699</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02886</t>
+          <t>CM-26-02899</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Corton Charlemagne</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Albert Bichot</t>
+          <t>Boillot Henri</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2'396.89</t>
+          <t>7'384.21</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.1848</v>
+        <v>0.0366</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0299</v>
+        <v>0.0922</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1228</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02879</t>
+          <t>CM-26-02911</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Canta la Perdiz</t>
+          <t>Corton Charlemagne</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Bodega Dominio del Aguila</t>
+          <t>Albert Bichot</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>3'570.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0446</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02847</t>
+          <t>CM-26-02894</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
+          <t>Chambertin</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Il Marroneto</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
@@ -2579,188 +2579,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>154</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02894</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Chambertin</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Armand Rousseau</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>155</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02846</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Il Marroneto</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>129</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-02839</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Il Marroneto</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N12"/>
+  <autoFilter ref="A3:N9"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -2775,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2797,14 +2617,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 15 Sep 2026)</t>
+          <t>📅 DELAYED OFFER WINNERS — Last 30 Days (since 19 Sep 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-15 14:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-19 09:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -2987,146 +2807,146 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>18'028.54</t>
+          <t>18'595.54</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
         <v>0.6977</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2251</v>
+        <v>0.2322</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5087</v>
+        <v>0.5115</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02785</t>
+          <t>CM-26-02745</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Barbaresco Crichët Pajé</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Roagna</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>4.76%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>23'281.93</t>
+          <t>22'989.15</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3527</v>
+        <v>0.2855</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2907</v>
+        <v>0.2871</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3279</v>
+        <v>0.2861</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02745</t>
+          <t>CM-26-02875</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>4.76%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>22'989.15</t>
+          <t>45'600.00</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.2855</v>
+        <v>0.066</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2871</v>
+        <v>0.5694</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2861</v>
+        <v>0.2674</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02875</t>
+          <t>CM-26-02698</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3136,57 +2956,57 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>45'600.00</t>
+          <t>44'496.24</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.066</v>
+        <v>0.0342</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5694</v>
+        <v>0.5556</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2674</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02698</t>
+          <t>CM-26-02785</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -3196,117 +3016,117 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Barbaresco Crichët Pajé</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Roagna</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>44'496.24</t>
+          <t>16'493.67</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0342</v>
+        <v>0.2352</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.5556</v>
+        <v>0.206</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.2428</v>
+        <v>0.2235</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02695</t>
+          <t>CM-26-02879</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Canta la Perdiz</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Bodega Dominio del Aguila</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>18'434.16</t>
+          <t>7'140.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.078</v>
+        <v>0.24</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2302</v>
+        <v>0.0892</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1389</v>
+        <v>0.1797</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02674</t>
+          <t>CM-26-02886</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -3316,117 +3136,117 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Hosanna</t>
+          <t>Corton Charlemagne</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Hosanna</t>
+          <t>Albert Bichot</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>3'800.32</t>
+          <t>3'533.01</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1764</v>
+        <v>0.2537</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0475</v>
+        <v>0.0441</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1248</v>
+        <v>0.1699</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02886</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Corton Charlemagne</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Albert Bichot</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2'396.89</t>
+          <t>18'434.16</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1848</v>
+        <v>0.078</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.2302</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1228</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02879</t>
+          <t>CM-26-02899</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -3436,117 +3256,117 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Canta la Perdiz</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Bodega Dominio del Aguila</t>
+          <t>Boillot Henri</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>3'570.00</t>
+          <t>7'384.21</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.12</v>
+        <v>0.0366</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0446</v>
+        <v>0.0922</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0898</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02682</t>
+          <t>CM-26-02810</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Côte Rôtie La Mouline</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>9'515.00</t>
+          <t>3'723.64</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.03</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1188</v>
+        <v>0.0465</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.063</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02810</t>
+          <t>CM-26-02847</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -3556,86 +3376,86 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mouline</t>
+          <t>Brunello di Montalcino Madonna delle Grazie</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Il Marroneto</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>3'723.64</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0465</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02847</t>
+          <t>CM-26-02911</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
+          <t>Corton Charlemagne</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Il Marroneto</t>
+          <t>Albert Bichot</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0</v>
@@ -3662,7 +3482,7 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -3695,7 +3515,7 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -3722,7 +3542,7 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
@@ -3782,7 +3602,7 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
@@ -3842,7 +3662,7 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
@@ -3900,68 +3720,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>158</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-02676</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Latour</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Château Latour</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N21"/>
+  <autoFilter ref="A3:N20"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3976,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N176"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4005,7 +3765,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-15 14:15  |  Scoring: 60% Conversion + 40% Sales</t>
+          <t>Generated: 2026-10-19 09:53  |  Scoring: 60% Conversion + 40% Sales</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4008,17 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>12'825.56</t>
+          <t>10'413.56</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1602</v>
+        <v>0.13</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.6641</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -4608,17 +4368,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>18'028.54</t>
+          <t>18'595.54</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
         <v>0.6977</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2251</v>
+        <v>0.2322</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5087</v>
+        <v>0.5115</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -5707,7 +5467,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02785</t>
+          <t>CM-26-00871</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -5717,48 +5477,48 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Barbaresco Crichët Pajé</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Roagna</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>5.26%</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>23'281.93</t>
+          <t>27'251.02</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.3527</v>
+        <v>0.3155</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.2907</v>
+        <v>0.3403</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.3279</v>
+        <v>0.3254</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -5767,58 +5527,58 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00871</t>
+          <t>CM-26-01535</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Chambolle Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Robert Groffier Père &amp; Fils</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>27'251.02</t>
+          <t>29'972.47</t>
         </is>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3155</v>
+        <v>0.2729</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.3403</v>
+        <v>0.3743</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3254</v>
+        <v>0.3135</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -5827,7 +5587,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01535</t>
+          <t>CM-26-00012</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -5837,48 +5597,48 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Chambolle Musigny Les Amoureuses</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Domaine Robert Groffier Père &amp; Fils</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>8.16%</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>29'972.47</t>
+          <t>3'517.88</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.2729</v>
+        <v>0.4895</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.3743</v>
+        <v>0.0439</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.3135</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -5887,58 +5647,58 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00012</t>
+          <t>CM-26-01525</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Gevrey Chambertin Clos St-Jacques</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>8.16%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>3'517.88</t>
+          <t>58'095.75</t>
         </is>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.4895</v>
+        <v>0.0324</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0439</v>
+        <v>0.7255</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3113</v>
+        <v>0.3096</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -5947,7 +5707,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01525</t>
+          <t>CM-26-01254</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -5957,48 +5717,48 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Clos St-Jacques</t>
+          <t>Bâtard-Montrachet</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>58'095.75</t>
+          <t>34'706.75</t>
         </is>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.0324</v>
+        <v>0.2142</v>
       </c>
       <c r="M35" s="6" t="n">
-        <v>0.7255</v>
+        <v>0.4334</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.3096</v>
+        <v>0.3019</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -6007,7 +5767,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01254</t>
+          <t>CM-26-01276</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -6017,48 +5777,48 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Bâtard-Montrachet</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>34'706.75</t>
+          <t>43'760.71</t>
         </is>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.2142</v>
+        <v>0.1332</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.4334</v>
+        <v>0.5465</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.3019</v>
+        <v>0.2985</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -6067,7 +5827,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01276</t>
+          <t>CM-26-02141</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -6077,48 +5837,48 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Chambertin Très Vieilles Vignes</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Bernard Dugat-Py</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>43'760.71</t>
+          <t>41'568.52</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.1332</v>
+        <v>0.15</v>
       </c>
       <c r="M37" s="6" t="n">
-        <v>0.5465</v>
+        <v>0.5191</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.2985</v>
+        <v>0.2976</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -6127,58 +5887,58 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02141</t>
+          <t>CM-26-02745</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Très Vieilles Vignes</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Domaine Bernard Dugat-Py</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>4.76%</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>41'568.52</t>
+          <t>22'989.15</t>
         </is>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.15</v>
+        <v>0.2855</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.5191</v>
+        <v>0.2871</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.2976</v>
+        <v>0.2861</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -6187,7 +5947,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02745</t>
+          <t>CM-26-02259</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -6197,48 +5957,48 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>Mouton Rothschild</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>4.76%</t>
+          <t>6.67%</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>22'989.15</t>
+          <t>7'140.00</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.2855</v>
+        <v>0.4001</v>
       </c>
       <c r="M39" s="6" t="n">
-        <v>0.2871</v>
+        <v>0.0892</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0.2861</v>
+        <v>0.2757</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -6247,7 +6007,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02259</t>
+          <t>CM-26-02440</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6257,48 +6017,48 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Mouton Rothschild</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Pavie</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>6.67%</t>
+          <t>4.27%</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>7'140.00</t>
+          <t>23'409.83</t>
         </is>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.4001</v>
+        <v>0.2561</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.0892</v>
+        <v>0.2923</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.2757</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -6307,58 +6067,58 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02440</t>
+          <t>CM-26-02875</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>23'409.83</t>
+          <t>45'600.00</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.2561</v>
+        <v>0.066</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>0.2923</v>
+        <v>0.5694</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0.2706</v>
+        <v>0.2674</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -6367,7 +6127,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02875</t>
+          <t>CM-26-00930</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6377,48 +6137,48 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>45'600.00</t>
+          <t>37'235.72</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.066</v>
+        <v>0.1278</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.5694</v>
+        <v>0.465</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.2674</v>
+        <v>0.2627</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -6427,7 +6187,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00930</t>
+          <t>CM-26-01928</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -6437,48 +6197,48 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Hudelot-Noëllat</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>37'235.72</t>
+          <t>37'210.94</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.1278</v>
+        <v>0.1176</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>0.465</v>
+        <v>0.4647</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0.2627</v>
+        <v>0.2564</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -6487,7 +6247,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01928</t>
+          <t>CM-26-00970</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6497,48 +6257,48 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Domaine Hudelot-Noëllat</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>37'210.94</t>
+          <t>36'300.00</t>
         </is>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.1176</v>
+        <v>0.1224</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.4647</v>
+        <v>0.4533</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.2564</v>
+        <v>0.2548</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -6547,7 +6307,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00970</t>
+          <t>CM-26-02698</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6557,48 +6317,48 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>36'300.00</t>
+          <t>44'496.24</t>
         </is>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0.1224</v>
+        <v>0.0342</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>0.4533</v>
+        <v>0.5556</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0.2548</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -6607,58 +6367,58 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02698</t>
+          <t>CM-26-01177</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Côte Rôtie La Turque</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Guigal</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>44'496.24</t>
+          <t>23'619.73</t>
         </is>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.1986</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.5556</v>
+        <v>0.295</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.2428</v>
+        <v>0.2372</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -6667,58 +6427,58 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01177</t>
+          <t>CM-26-02464</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Turque</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Domaine Guigal</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>181</v>
+        <v>475</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>23'619.73</t>
+          <t>44'390.76</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>0.1986</v>
+        <v>0.0252</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>0.295</v>
+        <v>0.5543</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>0.2372</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -6727,7 +6487,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02464</t>
+          <t>CM-26-02785</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -6737,48 +6497,48 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Barbaresco Crichët Pajé</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Roagna</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>475</v>
+        <v>51</v>
       </c>
       <c r="I48" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>44'390.76</t>
+          <t>16'493.67</t>
         </is>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.0252</v>
+        <v>0.2352</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.5543</v>
+        <v>0.206</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.2368</v>
+        <v>0.2235</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -7627,58 +7387,58 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02108</t>
+          <t>CM-26-02879</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Canta la Perdiz</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Bodega Dominio del Aguila</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
         <v>50</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>21'336.21</t>
+          <t>7'140.00</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>0.2664</v>
+        <v>0.0892</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>0.1786</v>
+        <v>0.1797</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -7687,7 +7447,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01494</t>
+          <t>CM-26-02108</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7697,48 +7457,48 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>17'751.48</t>
+          <t>21'336.21</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.1464</v>
+        <v>0.12</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.2217</v>
+        <v>0.2664</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.1765</v>
+        <v>0.1786</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -7747,58 +7507,58 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02431</t>
+          <t>CM-26-01494</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Monte Bello</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>Ridge Vineyards</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>11'961.88</t>
+          <t>17'751.48</t>
         </is>
       </c>
       <c r="L65" s="6" t="n">
-        <v>0.1926</v>
+        <v>0.1464</v>
       </c>
       <c r="M65" s="6" t="n">
-        <v>0.1494</v>
+        <v>0.2217</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>0.1753</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -7807,7 +7567,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01219</t>
+          <t>CM-25-02431</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7832,33 +7592,33 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>15'539.38</t>
+          <t>11'961.88</t>
         </is>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.1626</v>
+        <v>0.1926</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.194</v>
+        <v>0.1494</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.1752</v>
+        <v>0.1753</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -7867,58 +7627,58 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02144</t>
+          <t>CM-26-01219</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Gevrey Chambertin Lavaux St. Jacques</t>
+          <t>Monte Bello</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Ridge Vineyards</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>24</v>
+        <v>221</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>4'860.00</t>
+          <t>15'539.38</t>
         </is>
       </c>
       <c r="L67" s="6" t="n">
-        <v>0.2501</v>
+        <v>0.1626</v>
       </c>
       <c r="M67" s="6" t="n">
-        <v>0.0607</v>
+        <v>0.194</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>0.1743</v>
+        <v>0.1752</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -7927,58 +7687,58 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01582</t>
+          <t>CM-26-02144</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Les Cintres</t>
+          <t>Gevrey Chambertin Lavaux St. Jacques</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Philipponnat</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>940</v>
+        <v>24</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>24'219.63</t>
+          <t>4'860.00</t>
         </is>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.2501</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.3024</v>
+        <v>0.0607</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.1631</v>
+        <v>0.1743</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -7987,58 +7747,58 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02475</t>
+          <t>CM-26-02886</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie Cuvée Belle Helene</t>
+          <t>Corton Charlemagne</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Stéphane Ogier</t>
+          <t>Albert Bichot</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>1015</v>
+        <v>71</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>23'911.81</t>
+          <t>3'533.01</t>
         </is>
       </c>
       <c r="L69" s="6" t="n">
-        <v>0.0708</v>
+        <v>0.2537</v>
       </c>
       <c r="M69" s="6" t="n">
-        <v>0.2986</v>
+        <v>0.0441</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>0.1619</v>
+        <v>0.1699</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -8047,58 +7807,58 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00730</t>
+          <t>CM-26-01582</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>La Violette</t>
+          <t>Champagne Extra Brut Les Cintres</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Château La Violette</t>
+          <t>Philipponnat</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>95</v>
+        <v>940</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>16'003.16</t>
+          <t>24'219.63</t>
         </is>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.0702</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.1998</v>
+        <v>0.3024</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.1559</v>
+        <v>0.1631</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -8107,58 +7867,58 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02972</t>
+          <t>CM-26-02475</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Finca Piedra Infinita</t>
+          <t>Côte Rôtie Cuvée Belle Helene</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Familia Zuccardi</t>
+          <t>Stéphane Ogier</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>73</v>
+        <v>1015</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>1'277.97</t>
+          <t>23'911.81</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>0.2466</v>
+        <v>0.0708</v>
       </c>
       <c r="M71" s="6" t="n">
-        <v>0.016</v>
+        <v>0.2986</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>0.1544</v>
+        <v>0.1619</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -8167,58 +7927,58 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02689</t>
+          <t>CM-26-00730</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges la Perrière</t>
+          <t>La Violette</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Domaine Henri Gouges</t>
+          <t>Château La Violette</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>3'300.53</t>
+          <t>16'003.16</t>
         </is>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.222</v>
+        <v>0.1266</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.0412</v>
+        <v>0.1998</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.1497</v>
+        <v>0.1559</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -8227,58 +7987,58 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01163</t>
+          <t>CM-25-02972</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Finca Piedra Infinita</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Familia Zuccardi</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>24'206.56</t>
+          <t>1'277.97</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>0.0462</v>
+        <v>0.2466</v>
       </c>
       <c r="M73" s="6" t="n">
-        <v>0.3023</v>
+        <v>0.016</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>0.1486</v>
+        <v>0.1544</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -8287,7 +8047,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01500</t>
+          <t>CM-25-02689</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -8297,48 +8057,48 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Auxey-Duresses Les Hautés</t>
+          <t>Nuits Saint Georges la Perrière</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Domaine Pierre Vincent</t>
+          <t>Domaine Henri Gouges</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>3.74%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>2'246.57</t>
+          <t>3'300.53</t>
         </is>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.2244</v>
+        <v>0.222</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.0281</v>
+        <v>0.0412</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.1459</v>
+        <v>0.1497</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -8347,58 +8107,58 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00594</t>
+          <t>CM-26-01163</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Côte Rôtie La Mordorée</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Maison M. Chapoutier</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>12'780.81</t>
+          <t>24'206.56</t>
         </is>
       </c>
       <c r="L75" s="6" t="n">
-        <v>0.1362</v>
+        <v>0.0462</v>
       </c>
       <c r="M75" s="6" t="n">
-        <v>0.1596</v>
+        <v>0.3023</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>0.1456</v>
+        <v>0.1486</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -8407,58 +8167,58 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02409</t>
+          <t>CM-26-01500</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Tenuta Nuova</t>
+          <t>Auxey-Duresses Les Hautés</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Casanova di Neri</t>
+          <t>Domaine Pierre Vincent</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>380</v>
+        <v>107</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>12'911.34</t>
+          <t>2'246.57</t>
         </is>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.2244</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.1612</v>
+        <v>0.0281</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.1404</v>
+        <v>0.1459</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -8467,58 +8227,58 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02465</t>
+          <t>CM-26-00594</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Côte Rôtie La Mordorée</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Maison M. Chapoutier</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>248</v>
+        <v>88</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>24'929.00</t>
+          <t>12'780.81</t>
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>0.024</v>
+        <v>0.1362</v>
       </c>
       <c r="M77" s="6" t="n">
-        <v>0.3113</v>
+        <v>0.1596</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>0.1389</v>
+        <v>0.1456</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -8527,58 +8287,58 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02695</t>
+          <t>CM-26-02409</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Brunello di Montalcino Tenuta Nuova</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Casanova di Neri</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>18'434.16</t>
+          <t>12'911.34</t>
         </is>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.078</v>
+        <v>0.1266</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.2302</v>
+        <v>0.1612</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.1389</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -8587,58 +8347,58 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02637</t>
+          <t>CM-26-02465</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Hommage à Jacques Perrin</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Château de Beaucastel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>28</v>
+        <v>248</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>1'616.38</t>
+          <t>24'929.00</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>0.2142</v>
+        <v>0.024</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>0.0202</v>
+        <v>0.3113</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>0.1366</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -8647,7 +8407,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00675</t>
+          <t>CM-26-02695</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -8657,12 +8417,12 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -8672,33 +8432,33 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="I80" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>24'010.38</t>
+          <t>18'434.16</t>
         </is>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.0168</v>
+        <v>0.078</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.2998</v>
+        <v>0.2302</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.13</v>
+        <v>0.1389</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -8707,58 +8467,58 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02226</t>
+          <t>CM-25-02637</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>Hommage à Jacques Perrin</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Château de Beaucastel</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>9'090.00</t>
+          <t>1'616.38</t>
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>0.1398</v>
+        <v>0.2142</v>
       </c>
       <c r="M81" s="6" t="n">
-        <v>0.1135</v>
+        <v>0.0202</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>0.1293</v>
+        <v>0.1366</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -8767,58 +8527,58 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02674</t>
+          <t>CM-26-02226</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Hosanna</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Château Hosanna</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>3'800.32</t>
+          <t>9'090.00</t>
         </is>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.1764</v>
+        <v>0.1398</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.0475</v>
+        <v>0.1135</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.1248</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -8827,58 +8587,58 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01170</t>
+          <t>CM-26-02674</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Hosanna</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Hosanna</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>22'583.46</t>
+          <t>3'800.32</t>
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.1764</v>
       </c>
       <c r="M83" s="6" t="n">
-        <v>0.282</v>
+        <v>0.0475</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>0.1243</v>
+        <v>0.1248</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -8887,58 +8647,58 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02886</t>
+          <t>CM-26-01170</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Albert Bichot</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>2'396.89</t>
+          <t>22'583.46</t>
         </is>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.1848</v>
+        <v>0.0192</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.0299</v>
+        <v>0.282</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.1228</v>
+        <v>0.1243</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -10087,17 +9847,17 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02879</t>
+          <t>CM-26-01480</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Canta la Perdiz</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -10107,38 +9867,38 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Bodega Dominio del Aguila</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I104" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>3'570.00</t>
+          <t>7'370.74</t>
         </is>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.12</v>
+        <v>0.0882</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.092</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>0.0898</v>
+        <v>0.0897</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
@@ -10147,58 +9907,58 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01480</t>
+          <t>CM-26-02357</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>La Nieta</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Viñedos de Páganos</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>7'370.74</t>
+          <t>2'869.98</t>
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>0.0882</v>
+        <v>0.1146</v>
       </c>
       <c r="M105" s="6" t="n">
-        <v>0.092</v>
+        <v>0.0358</v>
       </c>
       <c r="N105" s="6" t="n">
-        <v>0.0897</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
@@ -10207,58 +9967,58 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02357</t>
+          <t>CM-25-03004</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>La Nieta</t>
+          <t>Porto Vintage Nacional</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Viñedos de Páganos</t>
+          <t>Quinta Do Noval</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="H106" s="4" t="n">
-        <v>157</v>
+        <v>476</v>
       </c>
       <c r="I106" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>2'869.98</t>
+          <t>10'547.81</t>
         </is>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.1146</v>
+        <v>0.0504</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.0358</v>
+        <v>0.1317</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
@@ -10267,58 +10027,58 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03004</t>
+          <t>CM-26-00658</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Porto Vintage Nacional</t>
+          <t>Assortment de Grands Crus (12 bottles)</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Quinta Do Noval</t>
+          <t>Domaine Ponsot</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>10'547.81</t>
+          <t>5'945.00</t>
         </is>
       </c>
       <c r="L107" s="6" t="n">
-        <v>0.0504</v>
+        <v>0.0882</v>
       </c>
       <c r="M107" s="6" t="n">
-        <v>0.1317</v>
+        <v>0.0742</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>0.0829</v>
+        <v>0.08260000000000001</v>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
@@ -10327,7 +10087,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00658</t>
+          <t>CM-25-02535</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -10337,48 +10097,48 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Assortment de Grands Crus (12 bottles)</t>
+          <t>Meursault Clos des Bouchers</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ponsot</t>
+          <t>Domaine Jean Marc Roulot</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H108" s="4" t="n">
-        <v>68</v>
+        <v>268</v>
       </c>
       <c r="I108" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>5'945.00</t>
+          <t>10'885.80</t>
         </is>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.0882</v>
+        <v>0.045</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.0742</v>
+        <v>0.1359</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0814</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
@@ -10387,17 +10147,17 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02535</t>
+          <t>CM-26-02514</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Meursault Clos des Bouchers</t>
+          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -10407,38 +10167,38 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Domaine Jean Marc Roulot</t>
+          <t>Veuve Clicquot Ponsardin</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>268</v>
+        <v>66</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>10'885.80</t>
+          <t>4'283.11</t>
         </is>
       </c>
       <c r="L109" s="6" t="n">
-        <v>0.045</v>
+        <v>0.0912</v>
       </c>
       <c r="M109" s="6" t="n">
-        <v>0.1359</v>
+        <v>0.0535</v>
       </c>
       <c r="N109" s="6" t="n">
-        <v>0.0814</v>
+        <v>0.0761</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
@@ -10447,58 +10207,58 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02514</t>
+          <t>CM-26-02593</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut La Grande Dame (Yayoi Kusama)</t>
+          <t>Bonnes-Mares</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Veuve Clicquot Ponsardin</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H110" s="4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I110" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>4'283.11</t>
+          <t>2'129.55</t>
         </is>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.0912</v>
+        <v>0.1032</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.0535</v>
+        <v>0.0266</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>0.0761</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
@@ -10507,58 +10267,58 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02593</t>
+          <t>CM-26-00483</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Bonnes-Mares</t>
+          <t>Pie Franco</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Bodegas Casa Castillo</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I111" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2'129.55</t>
+          <t>697.16</t>
         </is>
       </c>
       <c r="L111" s="6" t="n">
-        <v>0.1032</v>
+        <v>0.1134</v>
       </c>
       <c r="M111" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N111" s="6" t="n">
-        <v>0.0726</v>
+        <v>0.07149999999999999</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
@@ -10567,7 +10327,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00483</t>
+          <t>CM-25-02609</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -10577,48 +10337,48 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Pie Franco</t>
+          <t>Clos de la Roche</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Bodegas Casa Castillo</t>
+          <t>Domaine Georges Lignier</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H112" s="4" t="n">
-        <v>53</v>
+        <v>233</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>697.16</t>
+          <t>5'003.90</t>
         </is>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.1134</v>
+        <v>0.0774</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
@@ -10627,58 +10387,58 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02609</t>
+          <t>CM-26-02158</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Clos de la Roche</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Lignier</t>
+          <t>Domaine du Prieuré Roch</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>5'003.90</t>
+          <t>11'314.66</t>
         </is>
       </c>
       <c r="L113" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.0222</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>0.0625</v>
+        <v>0.1413</v>
       </c>
       <c r="N113" s="6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
@@ -10687,58 +10447,58 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02158</t>
+          <t>CM-26-02370</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Finca El Bosque</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Prieuré Roch</t>
+          <t>Viñedos y Bodegas Sierra Cantabria</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H114" s="4" t="n">
-        <v>273</v>
+        <v>54</v>
       </c>
       <c r="I114" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>11'314.66</t>
+          <t>603.91</t>
         </is>
       </c>
       <c r="L114" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.111</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>0.1413</v>
+        <v>0.0075</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>0.0698</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
@@ -10747,58 +10507,58 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02370</t>
+          <t>CM-26-02154</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Finca El Bosque</t>
+          <t>Morey St. Denis Clos de la Bussière</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>Viñedos y Bodegas Sierra Cantabria</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H115" s="6" t="n">
-        <v>54</v>
+        <v>290</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>603.91</t>
+          <t>7'898.70</t>
         </is>
       </c>
       <c r="L115" s="6" t="n">
-        <v>0.111</v>
+        <v>0.0414</v>
       </c>
       <c r="M115" s="6" t="n">
-        <v>0.0075</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="N115" s="6" t="n">
-        <v>0.0696</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
@@ -10807,58 +10567,58 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02154</t>
+          <t>CM-26-02682</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Morey St. Denis Clos de la Bussière</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H116" s="4" t="n">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>7'898.70</t>
+          <t>9'515.00</t>
         </is>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.0414</v>
+        <v>0.0258</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1188</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>0.0643</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
@@ -10867,58 +10627,58 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02682</t>
+          <t>CM-26-02899</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Boillot Henri</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="I117" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>9'515.00</t>
+          <t>7'384.21</t>
         </is>
       </c>
       <c r="L117" s="6" t="n">
-        <v>0.0258</v>
+        <v>0.0366</v>
       </c>
       <c r="M117" s="6" t="n">
-        <v>0.1188</v>
+        <v>0.0922</v>
       </c>
       <c r="N117" s="6" t="n">
-        <v>0.063</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
@@ -10968,17 +10728,17 @@
       </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>8'422.42</t>
+          <t>8'204.48</t>
         </is>
       </c>
       <c r="L118" s="4" t="n">
         <v>0.0276</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>0.1052</v>
+        <v>0.1025</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>0.0586</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
@@ -11887,7 +11647,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01167</t>
+          <t>CM-26-01288</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -11897,26 +11657,26 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H134" s="4" t="n">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="I134" s="4" t="n">
         <v>0</v>
@@ -11947,7 +11707,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01159</t>
+          <t>CM-26-01167</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -11957,17 +11717,17 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
@@ -11976,7 +11736,7 @@
         </is>
       </c>
       <c r="H135" s="6" t="n">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="I135" s="6" t="n">
         <v>0</v>
@@ -12007,7 +11767,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01158</t>
+          <t>CM-26-01159</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -12022,7 +11782,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -12032,11 +11792,11 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H136" s="4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I136" s="4" t="n">
         <v>0</v>
@@ -12067,7 +11827,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01288</t>
+          <t>CM-26-01158</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -12077,26 +11837,26 @@
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G137" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H137" s="6" t="n">
-        <v>240</v>
+        <v>26</v>
       </c>
       <c r="I137" s="6" t="n">
         <v>0</v>
@@ -12427,7 +12187,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03397</t>
+          <t>CM-25-02472</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -12437,26 +12197,26 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Clos de Vougeot</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Leroy</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="I143" s="6" t="n">
         <v>0</v>
@@ -12607,7 +12367,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00593</t>
+          <t>CM-26-00675</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -12617,26 +12377,26 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Domaine du Comte Liger-Belair</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H146" s="4" t="n">
-        <v>129</v>
+        <v>362</v>
       </c>
       <c r="I146" s="4" t="n">
         <v>0</v>
@@ -12667,7 +12427,7 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>CM-25-03538</t>
+          <t>CM-26-00593</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
@@ -12677,26 +12437,26 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>DRC Grands Echézeaux</t>
+          <t>Assortment Grand Cru 3x150cl (1x Clos de Vougeot, 1x Echezeaux, 1x La Romanée)</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine du Comte Liger-Belair</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I147" s="6" t="n">
         <v>0</v>
@@ -12727,7 +12487,7 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>CM-25-03537</t>
+          <t>CM-25-03538</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -12737,12 +12497,12 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>DRC Grands Echézeaux</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -12756,7 +12516,7 @@
         </is>
       </c>
       <c r="H148" s="4" t="n">
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="I148" s="4" t="n">
         <v>0</v>
@@ -12787,7 +12547,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02825</t>
+          <t>CM-25-03537</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -12797,26 +12557,26 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Vosne Romanée Cros Parantoux</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>Rouget Emmanuel</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G149" s="6" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H149" s="6" t="n">
-        <v>643</v>
+        <v>252</v>
       </c>
       <c r="I149" s="6" t="n">
         <v>0</v>
@@ -12847,7 +12607,7 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>CM-25-02800</t>
+          <t>CM-25-03397</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -12857,26 +12617,26 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Redigaffi 7 (Limited Edition)</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Tua Rita</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H150" s="4" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I150" s="4" t="n">
         <v>0</v>
@@ -12907,7 +12667,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>CM-25-02472</t>
+          <t>CM-25-02825</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -12917,26 +12677,26 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Clos de Vougeot</t>
+          <t>Vosne Romanée Cros Parantoux</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leroy</t>
+          <t>Rouget Emmanuel</t>
         </is>
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
-        <v>116</v>
+        <v>643</v>
       </c>
       <c r="I151" s="6" t="n">
         <v>0</v>
@@ -12967,36 +12727,36 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01341</t>
+          <t>CM-25-02800</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Redigaffi 7 (Limited Edition)</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Cathiard Vineyard</t>
+          <t>Azienda Agricola Tua Rita</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H152" s="4" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="I152" s="4" t="n">
         <v>0</v>
@@ -13027,36 +12787,36 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01310</t>
+          <t>CM-26-01341</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>Domaine Georges Roumier</t>
+          <t>Cathiard Vineyard</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
-        <v>716</v>
+        <v>91</v>
       </c>
       <c r="I153" s="6" t="n">
         <v>0</v>
@@ -13087,36 +12847,36 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02847</t>
+          <t>CM-26-01310</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Il Marroneto</t>
+          <t>Domaine Georges Roumier</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
-        <v>115</v>
+        <v>716</v>
       </c>
       <c r="I154" s="4" t="n">
         <v>0</v>
@@ -13147,7 +12907,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01349</t>
+          <t>CM-26-02847</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -13157,26 +12917,26 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Brunello di Montalcino Madonna delle Grazie</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>Domaine Bruno Clair</t>
+          <t>Il Marroneto</t>
         </is>
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="I155" s="6" t="n">
         <v>0</v>
@@ -13207,36 +12967,36 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01477</t>
+          <t>CM-26-01349</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Chambolle-Musigny Les Amoureuses</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine Bruno Clair</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H156" s="4" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I156" s="4" t="n">
         <v>0</v>
@@ -13267,7 +13027,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02894</t>
+          <t>CM-26-02220</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -13277,26 +13037,26 @@
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Chambertin</t>
+          <t>Chevalier Montrachet</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Domaine Leflaive</t>
         </is>
       </c>
       <c r="G157" s="6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H157" s="6" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="I157" s="6" t="n">
         <v>0</v>
@@ -13327,17 +13087,17 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02846</t>
+          <t>CM-26-02911</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
+          <t>Corton Charlemagne</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -13347,16 +13107,16 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Il Marroneto</t>
+          <t>Albert Bichot</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H158" s="4" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="I158" s="4" t="n">
         <v>0</v>
@@ -13387,36 +13147,36 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02839</t>
+          <t>CM-26-02894</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Madonna delle Grazie</t>
+          <t>Chambertin</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>Il Marroneto</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G159" s="6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H159" s="6" t="n">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="I159" s="6" t="n">
         <v>0</v>
@@ -13447,36 +13207,36 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02802</t>
+          <t>CM-26-02846</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>DRC Assortment Case 12 Bottles (1RC, 3LT, 2RI, 2E, 3RSV, 1GE)</t>
+          <t>Brunello di Montalcino Madonna delle Grazie</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Il Marroneto</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H160" s="4" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="I160" s="4" t="n">
         <v>0</v>
@@ -13507,36 +13267,36 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02676</t>
+          <t>CM-26-02839</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Brunello di Montalcino Madonna delle Grazie</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Il Marroneto</t>
         </is>
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H161" s="6" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="I161" s="6" t="n">
         <v>0</v>
@@ -13567,7 +13327,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02605</t>
+          <t>CM-26-02802</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -13577,22 +13337,26 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="inlineStr"/>
+          <t>DRC Assortment Case 12 Bottles (1RC, 3LT, 2RI, 2E, 3RSV, 1GE)</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H162" s="4" t="n">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="I162" s="4" t="n">
         <v>0</v>
@@ -13623,7 +13387,7 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02463</t>
+          <t>CM-26-02676</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -13633,26 +13397,26 @@
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H163" s="6" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="I163" s="6" t="n">
         <v>0</v>
@@ -13683,7 +13447,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02406</t>
+          <t>CM-26-02605</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -13693,26 +13457,22 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
+          <t>Vertical Mouton Rothschild 1 x 150cl each vintage from 1995 to 2024</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr"/>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H164" s="4" t="n">
-        <v>775</v>
+        <v>168</v>
       </c>
       <c r="I164" s="4" t="n">
         <v>0</v>
@@ -13743,7 +13503,7 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02220</t>
+          <t>CM-26-02463</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -13753,26 +13513,26 @@
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Chevalier Montrachet</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>Domaine Leflaive</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H165" s="6" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I165" s="6" t="n">
         <v>0</v>
@@ -13803,36 +13563,36 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>CM-26-02073</t>
+          <t>CM-26-02406</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Richebourg</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>Domaine Méo-Camuzet</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H166" s="4" t="n">
-        <v>223</v>
+        <v>775</v>
       </c>
       <c r="I166" s="4" t="n">
         <v>0</v>
@@ -13863,12 +13623,12 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>CM-26-02062</t>
+          <t>CM-26-02073</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
@@ -13878,7 +13638,7 @@
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
@@ -13888,11 +13648,11 @@
       </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H167" s="6" t="n">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="I167" s="6" t="n">
         <v>0</v>
@@ -13923,36 +13683,36 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01981</t>
+          <t>CM-26-01477</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Kayli Morgan Vineyard</t>
+          <t>Chambolle-Musigny Les Amoureuses</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>Hundred Acre</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H168" s="4" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="I168" s="4" t="n">
         <v>0</v>
@@ -13983,7 +13743,7 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01680</t>
+          <t>CM-26-02062</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -13993,26 +13753,26 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>DRC Richebourg</t>
+          <t>Richebourg</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Domaine Méo-Camuzet</t>
         </is>
       </c>
       <c r="G169" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H169" s="6" t="n">
-        <v>239</v>
+        <v>47</v>
       </c>
       <c r="I169" s="6" t="n">
         <v>0</v>
@@ -14043,36 +13803,36 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01614</t>
+          <t>CM-26-01981</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>DRC la Tâche</t>
+          <t>Kayli Morgan Vineyard</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Hundred Acre</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H170" s="4" t="n">
-        <v>613</v>
+        <v>28</v>
       </c>
       <c r="I170" s="4" t="n">
         <v>0</v>
@@ -14103,36 +13863,36 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01513</t>
+          <t>CM-26-01680</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>DRC Richebourg</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G171" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H171" s="6" t="n">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="I171" s="6" t="n">
         <v>0</v>
@@ -14163,7 +13923,7 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01512</t>
+          <t>CM-26-01614</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -14173,26 +13933,26 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>DRC la Tâche</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H172" s="4" t="n">
-        <v>20</v>
+        <v>613</v>
       </c>
       <c r="I172" s="4" t="n">
         <v>0</v>
@@ -14223,27 +13983,27 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01508</t>
+          <t>CM-26-01513</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Mugnier Jacques-Frederic</t>
         </is>
       </c>
       <c r="G173" s="6" t="inlineStr">
@@ -14252,7 +14012,7 @@
         </is>
       </c>
       <c r="H173" s="6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I173" s="6" t="n">
         <v>0</v>
@@ -14283,22 +14043,22 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01482</t>
+          <t>CM-26-01512</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Nuits Saint Georges Clos de la Marechale</t>
+          <t>Bonnes Mares</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -14308,11 +14068,11 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H174" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I174" s="4" t="n">
         <v>0</v>
@@ -14343,7 +14103,7 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01479</t>
+          <t>CM-26-01508</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -14353,26 +14113,26 @@
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Bonnes Mares</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>Mugnier Jacques-Frederic</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H175" s="6" t="n">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="I175" s="6" t="n">
         <v>0</v>
@@ -14403,62 +14163,182 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
+          <t>CM-26-01482</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>💎</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Nuits Saint Georges Clos de la Marechale</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="6" t="n">
+        <v>174</v>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>CM-26-01479</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Bonnes Mares</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>Mugnier Jacques-Frederic</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="n">
+        <v>152</v>
+      </c>
+      <c r="I177" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
           <t>CM-25-02438</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>🟣</t>
         </is>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>DRC Romanée Conti</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="E178" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="F178" s="4" t="inlineStr">
         <is>
           <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>2025-09-15</t>
         </is>
       </c>
-      <c r="H176" s="4" t="n">
+      <c r="H178" s="4" t="n">
         <v>410</v>
       </c>
-      <c r="I176" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="I178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="K176" s="4" t="inlineStr">
+      <c r="K178" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="L176" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M176" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N176" s="4" t="n">
+      <c r="L178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N176"/>
+  <autoFilter ref="A3:N178"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
